--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements_RTM'!$A$1:$O$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test_Cases'!$A$1:$K$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Assumptions_Decisions'!$A$1:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Assumptions_Decisions'!$A$1:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Implementation_Tasks'!$A$1:$I$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'State_Transitions'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Glossary'!$A$1:$B$16</definedName>
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="B2:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,6 @@
     <col width="4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -703,7 +702,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -724,7 +722,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>0.1 (Draft for review)</t>
+          <t>0.2 (Draft for review) — see SRS revision history</t>
         </is>
       </c>
     </row>
@@ -764,7 +762,18 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Last updated</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24 — architecture phase: ARCHITECTURE.md, ERD.md, ADR-0001…0012</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -844,7 +853,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1010,7 +1018,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1227,7 +1234,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -8101,7 +8107,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="N86" s="16" t="inlineStr"/>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>Mechanism designed: ARCHITECTURE.md §7, ADR-0006</t>
+        </is>
+      </c>
       <c r="O86" s="16" t="inlineStr"/>
       <c r="P86" s="4">
         <f>","&amp;SUBSTITUTE(F86," ","")&amp;","</f>
@@ -10926,10 +10936,14 @@
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N126" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N126" s="16" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md §3–4, §12; docs/ERD.md §1</t>
+        </is>
+      </c>
       <c r="O126" s="16" t="inlineStr"/>
       <c r="P126" s="4">
         <f>","&amp;SUBSTITUTE(F126," ","")&amp;","</f>
@@ -10995,10 +11009,14 @@
       </c>
       <c r="M127" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N127" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N127" s="16" t="inlineStr">
+        <is>
+          <t>docs/adr/0001–0012 (README summary pending, T-24)</t>
+        </is>
+      </c>
       <c r="O127" s="16" t="inlineStr"/>
       <c r="P127" s="4">
         <f>","&amp;SUBSTITUTE(F127," ","")&amp;","</f>
@@ -11765,7 +11783,11 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="N138" s="16" t="inlineStr"/>
+      <c r="N138" s="16" t="inlineStr">
+        <is>
+          <t>SRS v0.2 revision 2026-09-24</t>
+        </is>
+      </c>
       <c r="O138" s="16" t="inlineStr"/>
       <c r="P138" s="4">
         <f>","&amp;SUBSTITUTE(F138," ","")&amp;","</f>
@@ -14182,7 +14204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15510,7 +15532,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>PostgreSQL is recommended as the DBMS. The final choice and justification belong to the architecture phase.</t>
+          <t>The DBMS is PostgreSQL 16 (ADR-0002).</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -15520,12 +15542,12 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>MySQL, SQLite</t>
+          <t>MySQL, SQLite, MongoDB</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>DC-03, NFR-CON-04</t>
+          <t>DC-03, NFR-CON-04, ADR-0002</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -15543,38 +15565,42 @@
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>PRD inconsistency</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>The PRD mandates a master branch, but the repository was initialised with main.</t>
+          <t>The system is a modular monolith: Next.js web + one Express API + PostgreSQL (ADR-0001).</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>Create master and use it as the integration branch (DR-01).</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr"/>
+          <t>Every invariant fits in one ACID transaction, with no distributed consistency (PRD §9).</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Next.js-only; microservices</t>
+        </is>
+      </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>DR-01</t>
+          <t>DC-05, DR-14</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr"/>
@@ -15582,200 +15608,642 @@
     <row r="34" ht="33" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>The API is built with Express 5 + TypeScript (ADR-0003).</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>No hidden control flow, a large ecosystem, and explicit layering that is simple to trace and maintain.</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>NestJS; Fastify</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>DC-02, DC-07</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Chosen by product owner in architecture session</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>Data access uses Prisma, with CHECK constraints, partial unique indexes and triggers in hand-written SQL migrations (ADR-0004).</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Type-safe DX for most queries. Raw SQL is visible exactly where the integrity guarantees are implemented.</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Drizzle; Knex; TypeORM</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>NFR-CON-04, NFR-POR-03, NFR-SEC-08</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Chosen by product owner in architecture session</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>D-17</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Auth uses opaque DB-backed sessions (SHA-256 hash stored) in an httpOnly cookie, behind a same-origin Next.js /api proxy (ADR-0005).</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Real logout; a DB leak exposes no usable tokens; first-party cookies across different hosts.</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>JWT in cookie; Auth.js/Lucia</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>FR-AUTH-02, FR-AUTH-03, NFR-SEC-06</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Chosen by product owner in architecture session</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>D-18</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Concurrency uses row locks in the fixed order driver → pool → ride → wallet, compare-and-set transitions and DB constraints. Expiry is checked in the accept CAS, plus a 60 s in-process sweeper (ADR-0006).</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Deterministic outcome for the last-seat race, with no extra infrastructure.</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>Optimistic versioning; SERIALIZABLE; Redis lock</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>NFR-CON-01, NFR-CON-02, NFR-CON-03, NFR-REL-04</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38" ht="33" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>D-19</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>The repo is an npm-workspaces monorepo: apps/web, apps/api, packages/shared (Zod, enums, transition tables) (ADR-0008).</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>One source for schemas, enums and transition tables across web and API.</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>Turborepo/Nx; two repos</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>NFR-MNT-01, NFR-MNT-03</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>D-20</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Deployment is Docker Compose now, then Vercel + Railway + Supabase on free tiers, with a verify-no-payment guardrail (ADR-0009).</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>The primary run path (docker compose up) never depends on third parties, and the same images run in the cloud.</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Render-only; Vercel + Render + Neon</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>NFR-POR-01, NFR-POR-04, DC-04, DR-11</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>Chosen by product owner in architecture session</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>D-21</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Tests use Vitest + Supertest against a real PostgreSQL test DB (ADR-0011).</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Locks and constraints can only be proven against the real engine.</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Jest; mocks/SQLite; Testcontainers</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>DR-10, NFR-MNT-04</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41" ht="33" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>The frontend uses the Next.js App Router + TanStack Query (polling) + react-hook-form + Tailwind CSS (ADR-0012).</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Built-in loading/error states and polling; a small, maintainable UI stack.</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Vite + React Router; SWR; component libraries</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>DC-01, FR-PAX-07, NFR-USA-01</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>D-23</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Schema choices: pool_members link table, pools.capacity snapshot, driver_profiles table, zone code natural key, UUID ids, polymorphic append-only status_history (ERD §8).</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Row-local CHECK for capacity, re-matching history, driver-only ownership that is structural.</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>ride_requests.pool_id; capacity via trigger; driver columns on users</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>FR-POOL-02, FR-POOL-10, FR-HIST-02</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43" ht="33" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>PRD inconsistency</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>The PRD mandates a master branch, but the repository was initialised with main.</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Create master and use it as the integration branch (DR-01).</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>DR-01</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="33" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
           <t>P-02</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>PRD inconsistency</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>PRD §18 refers to "the concurrency problem in Section 14". It is actually in §12.</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>Treated as §12.</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr"/>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>NFR-CON-01</t>
         </is>
       </c>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="I44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="33" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>P-03</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>PRD inconsistency</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>The PRD lifecycle mixes passenger-level and trip-level states.</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D45" s="17" t="inlineStr">
         <is>
           <t>Split into two state machines (D-12).</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr"/>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>§5</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36" ht="33" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="I45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="33" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>OI-01</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>Open issue</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Choose the backend framework, ORM, auth mechanism, test framework, styling and hosting, each justified per DC-07.</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Resolve in: Architecture phase</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Resolved 2026-09-24: D-14…D-22, ADR-0001…0012</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>DC-07, DR-07</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="48" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>OI-02</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Open issue</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C47" s="17" t="inlineStr">
         <is>
           <t>Choose the concrete concurrency mechanism (pessimistic SELECT … FOR UPDATE versus a conditional update guarded by CHECK) and document it.</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Resolve in: Architecture phase</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr"/>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Resolved 2026-09-24: row locks + CAS + constraints in layers (D-18, ADR-0006)</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>NFR-CON-03</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>OI-03</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>Open issue</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>Decide whether the request-expiry sweeper runs as an in-process interval or lazily on read (NFR-REL-04 requires lazy correctness either way).</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Resolve in: Architecture phase</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr"/>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Resolved 2026-09-24: expiry checked in accept CAS, plus 60 s in-process sweeper (D-18)</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>NFR-REL-04</t>
         </is>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="inlineStr"/>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I38"/>
+  <autoFilter ref="A1:I48"/>
   <conditionalFormatting sqref="G2:G237">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>$G2="Proposed"</formula>
@@ -15905,7 +16373,11 @@
         </is>
       </c>
       <c r="H2" s="16" t="inlineStr"/>
-      <c r="I2" s="16" t="inlineStr"/>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>SRS v0.2 synced with ERD on 2026-09-24</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="33" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -15938,11 +16410,19 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr"/>
-      <c r="I3" s="16" t="inlineStr"/>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md, docs/ERD.md, docs/adr/0001–0012</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>Drafted 2026-09-24; awaiting review</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="33" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
@@ -17611,7 +18091,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -17799,7 +18278,6 @@
       <c r="G28" s="19" t="inlineStr"/>
       <c r="H28" s="19" t="inlineStr"/>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -18216,7 +18694,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -18651,7 +19128,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -18713,7 +19189,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -18766,8 +19241,6 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -19326,7 +19799,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="B2:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,6 @@
     <col width="4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -703,7 +702,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -772,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — same-gender ride option (BR-18) added; architecture phase docs (ARCHITECTURE.md, ERD.md, ADR-0001…0012)</t>
+          <t>2026-09-24 — Phase 0 (feature/project-setup): monorepo, conventions, API foundation, Docker</t>
         </is>
       </c>
     </row>
@@ -855,7 +853,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1021,7 +1018,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1238,7 +1234,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3302,7 +3297,7 @@
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>feature/driver-flow, feature/driver-ui</t>
+          <t>feature/tesla-pooling, feature/driver-ui</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
@@ -3375,7 +3370,7 @@
       </c>
       <c r="L21" s="17" t="inlineStr">
         <is>
-          <t>feature/driver-flow, feature/driver-ui</t>
+          <t>feature/tesla-pooling, feature/driver-ui</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr">
@@ -3448,7 +3443,7 @@
       </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t>feature/driver-flow</t>
+          <t>feature/tesla-pooling</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
@@ -3521,7 +3516,7 @@
       </c>
       <c r="L23" s="17" t="inlineStr">
         <is>
-          <t>feature/driver-flow, feature/driver-ui</t>
+          <t>feature/tesla-pooling, feature/driver-ui</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr">
@@ -7845,10 +7840,14 @@
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N82" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>ZodError → VALIDATION_ERROR mapping in error handler; schemas per endpoint later</t>
+        </is>
+      </c>
       <c r="O82" s="16" t="inlineStr"/>
       <c r="P82" s="4">
         <f>","&amp;SUBSTITUTE(F82," ","")&amp;","</f>
@@ -7918,10 +7917,14 @@
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N83" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>.gitignore excludes .env; .env.example placeholders only — commits f221565, 7d59b8d</t>
+        </is>
+      </c>
       <c r="O83" s="16" t="inlineStr"/>
       <c r="P83" s="4">
         <f>","&amp;SUBSTITUTE(F83," ","")&amp;","</f>
@@ -7991,10 +7994,14 @@
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N84" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>helmet headers + CORS to WEB_ORIGIN done; session cookie flags in feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O84" s="16" t="inlineStr"/>
       <c r="P84" s="4">
         <f>","&amp;SUBSTITUTE(F84," ","")&amp;","</f>
@@ -8214,10 +8221,14 @@
       </c>
       <c r="M87" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N87" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N87" s="16" t="inlineStr">
+        <is>
+          <t>Generic INTERNAL_ERROR message; details only in logs — commit 51da796</t>
+        </is>
+      </c>
       <c r="O87" s="16" t="inlineStr"/>
       <c r="P87" s="4">
         <f>","&amp;SUBSTITUTE(F87," ","")&amp;","</f>
@@ -8729,10 +8740,14 @@
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N94" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N94" s="16" t="inlineStr">
+        <is>
+          <t>middleware/error-handler.ts; test/app.test.ts — commit 51da796</t>
+        </is>
+      </c>
       <c r="O94" s="16" t="inlineStr"/>
       <c r="P94" s="4">
         <f>","&amp;SUBSTITUTE(F94," ","")&amp;","</f>
@@ -8802,10 +8817,14 @@
       </c>
       <c r="M95" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N95" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N95" s="16" t="inlineStr">
+        <is>
+          <t>/health + compose health checks — commits 51da796, 7d59b8d</t>
+        </is>
+      </c>
       <c r="O95" s="16" t="inlineStr"/>
       <c r="P95" s="4">
         <f>","&amp;SUBSTITUTE(F95," ","")&amp;","</f>
@@ -9678,10 +9697,14 @@
       </c>
       <c r="M107" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N107" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N107" s="16" t="inlineStr">
+        <is>
+          <t>docker compose up works (3 healthy); migrations/seed arrive in feature/db-schema</t>
+        </is>
+      </c>
       <c r="O107" s="16" t="inlineStr"/>
       <c r="P107" s="4">
         <f>","&amp;SUBSTITUTE(F107," ","")&amp;","</f>
@@ -9747,10 +9770,14 @@
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N108" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N108" s="16" t="inlineStr">
+        <is>
+          <t>config/env.ts, config/rules.ts, .env.example — commits 9ddba2e, 51da796, 7d59b8d</t>
+        </is>
+      </c>
       <c r="O108" s="16" t="inlineStr"/>
       <c r="P108" s="4">
         <f>","&amp;SUBSTITUTE(F108," ","")&amp;","</f>
@@ -9962,10 +9989,14 @@
       </c>
       <c r="M111" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N111" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N111" s="16" t="inlineStr">
+        <is>
+          <t>logger.ts, middleware/http-logger.ts — commits 51da796, 28caad4</t>
+        </is>
+      </c>
       <c r="O111" s="16" t="inlineStr"/>
       <c r="P111" s="4">
         <f>","&amp;SUBSTITUTE(F111," ","")&amp;","</f>
@@ -10100,10 +10131,14 @@
       </c>
       <c r="M113" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N113" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N113" s="16" t="inlineStr">
+        <is>
+          <t>pino redaction; headers not logged — commit 28caad4</t>
+        </is>
+      </c>
       <c r="O113" s="16" t="inlineStr"/>
       <c r="P113" s="4">
         <f>","&amp;SUBSTITUTE(F113," ","")&amp;","</f>
@@ -10169,10 +10204,14 @@
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N114" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="inlineStr">
+        <is>
+          <t>Module template documented (CODING_CONVENTIONS §4); health module follows it</t>
+        </is>
+      </c>
       <c r="O114" s="16" t="inlineStr"/>
       <c r="P114" s="4">
         <f>","&amp;SUBSTITUTE(F114," ","")&amp;","</f>
@@ -10311,10 +10350,14 @@
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N116" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N116" s="16" t="inlineStr">
+        <is>
+          <t>TypeScript strict, ESLint (simplicity rules), Prettier — commit f221565</t>
+        </is>
+      </c>
       <c r="O116" s="16" t="inlineStr"/>
       <c r="P116" s="4">
         <f>","&amp;SUBSTITUTE(F116," ","")&amp;","</f>
@@ -10380,10 +10423,14 @@
       </c>
       <c r="M117" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N117" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N117" s="16" t="inlineStr">
+        <is>
+          <t>npm test at root and in Docker (docker compose run --rm api npm test)</t>
+        </is>
+      </c>
       <c r="O117" s="16" t="inlineStr"/>
       <c r="P117" s="4">
         <f>","&amp;SUBSTITUTE(F117," ","")&amp;","</f>
@@ -10449,10 +10496,14 @@
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N118" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N118" s="16" t="inlineStr">
+        <is>
+          <t>apps/web: Next.js App Router</t>
+        </is>
+      </c>
       <c r="O118" s="16" t="inlineStr"/>
       <c r="P118" s="4">
         <f>","&amp;SUBSTITUTE(F118," ","")&amp;","</f>
@@ -10518,10 +10569,14 @@
       </c>
       <c r="M119" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N119" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N119" s="16" t="inlineStr">
+        <is>
+          <t>apps/api: Node.js + Express 5</t>
+        </is>
+      </c>
       <c r="O119" s="16" t="inlineStr"/>
       <c r="P119" s="4">
         <f>","&amp;SUBSTITUTE(F119," ","")&amp;","</f>
@@ -10587,10 +10642,14 @@
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N120" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N120" s="16" t="inlineStr">
+        <is>
+          <t>PostgreSQL 16 container</t>
+        </is>
+      </c>
       <c r="O120" s="16" t="inlineStr"/>
       <c r="P120" s="4">
         <f>","&amp;SUBSTITUTE(F120," ","")&amp;","</f>
@@ -10725,10 +10784,14 @@
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N122" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="inlineStr">
+        <is>
+          <t>Three containers only: db, api, web</t>
+        </is>
+      </c>
       <c r="O122" s="16" t="inlineStr"/>
       <c r="P122" s="4">
         <f>","&amp;SUBSTITUTE(F122," ","")&amp;","</f>
@@ -10794,10 +10857,14 @@
       </c>
       <c r="M123" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N123" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N123" s="16" t="inlineStr">
+        <is>
+          <t>No third-party runtime services</t>
+        </is>
+      </c>
       <c r="O123" s="16" t="inlineStr"/>
       <c r="P123" s="4">
         <f>","&amp;SUBSTITUTE(F123," ","")&amp;","</f>
@@ -11508,10 +11575,14 @@
       </c>
       <c r="M133" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N133" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N133" s="16" t="inlineStr">
+        <is>
+          <t>docker-compose.yml and .env.example added; migrations/seed in feature/db-schema</t>
+        </is>
+      </c>
       <c r="O133" s="16" t="inlineStr"/>
       <c r="P133" s="4">
         <f>","&amp;SUBSTITUTE(F133," ","")&amp;","</f>
@@ -13933,11 +14004,19 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr"/>
-      <c r="K35" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/app.test.ts (404, malformed JSON, requestId); 409/500 cases added with later modules</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="33" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
@@ -17245,11 +17324,19 @@
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="inlineStr"/>
-      <c r="I4" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>f221565 chore(repo), 9ddba2e docs(conventions) on feature/project-setup</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Also added docs/CODING_CONVENTIONS.md and config/rules.ts</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -17282,11 +17369,19 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="inlineStr"/>
-      <c r="I5" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>51da796 feat(api), 28caad4 refactor(api) on feature/project-setup</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Tests: apps/api/test/app.test.ts</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="33" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -17319,11 +17414,19 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>7d59b8d build(docker) on feature/project-setup</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Verified: 3 containers healthy, web page shows 'API ok', tests pass in container</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -17629,7 +17732,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>feature/driver-flow</t>
+          <t>feature/tesla-pooling</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -17656,7 +17759,11 @@
         </is>
       </c>
       <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Moved from feature/driver-flow: accept needs driver availability first (plan Phase 5)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="63" customHeight="1">
       <c r="A16" s="14" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 0 (feature/project-setup): monorepo, conventions, API foundation, Docker</t>
+          <t>2026-09-24 — Phase 1 (feature/db-schema): schema, integrity migration, db helpers, seed, constraint tests</t>
         </is>
       </c>
     </row>
@@ -2361,10 +2361,14 @@
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Jashim/Bullet and Kamal/Toofan seeded — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O7" s="16" t="inlineStr"/>
       <c r="P7" s="4">
         <f>","&amp;SUBSTITUTE(F7," ","")&amp;","</f>
@@ -4835,10 +4839,14 @@
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N41" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>pool_members_one_active_membership index tested; accept flow in feature/tesla-pooling — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O41" s="16" t="inlineStr"/>
       <c r="P41" s="4">
         <f>","&amp;SUBSTITUTE(F41," ","")&amp;","</f>
@@ -4908,10 +4916,14 @@
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>pool_members table; roster endpoint in feature/driver-flow — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O42" s="16" t="inlineStr"/>
       <c r="P42" s="4">
         <f>","&amp;SUBSTITUTE(F42," ","")&amp;","</f>
@@ -5500,10 +5512,14 @@
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N50" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>All money columns BIGINT paisa; formatting in UI later — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O50" s="16" t="inlineStr"/>
       <c r="P50" s="4">
         <f>","&amp;SUBSTITUTE(F50," ","")&amp;","</f>
@@ -5938,10 +5954,14 @@
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N56" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>wallets_balance_check + append-only ledger tested; settlement in feature/teslapay-wallet — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O56" s="16" t="inlineStr"/>
       <c r="P56" s="4">
         <f>","&amp;SUBSTITUTE(F56," ","")&amp;","</f>
@@ -6084,10 +6104,14 @@
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N58" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Append-only trigger tested; audit writer in feature/ride-request — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O58" s="16" t="inlineStr"/>
       <c r="P58" s="4">
         <f>","&amp;SUBSTITUTE(F58," ","")&amp;","</f>
@@ -6741,10 +6765,14 @@
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N67" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>prisma/seed-data/zones.ts; symmetry test — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O67" s="16" t="inlineStr"/>
       <c r="P67" s="4">
         <f>","&amp;SUBSTITUTE(F67," ","")&amp;","</f>
@@ -7252,10 +7280,14 @@
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N74" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>BIGINT *_paisa columns; db/money.ts exact conversion — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O74" s="16" t="inlineStr"/>
       <c r="P74" s="4">
         <f>","&amp;SUBSTITUTE(F74," ","")&amp;","</f>
@@ -8144,12 +8176,12 @@
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="N86" s="16" t="inlineStr">
         <is>
-          <t>Mechanism designed: ARCHITECTURE.md §7, ADR-0006</t>
+          <t>Prisma query API + tagged $queryRaw only — feature/db-schema</t>
         </is>
       </c>
       <c r="O86" s="16" t="inlineStr"/>
@@ -8521,10 +8553,14 @@
       </c>
       <c r="M91" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N91" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N91" s="16" t="inlineStr">
+        <is>
+          <t>Partial unique indexes; test/db/constraints.test.ts — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O91" s="16" t="inlineStr"/>
       <c r="P91" s="4">
         <f>","&amp;SUBSTITUTE(F91," ","")&amp;","</f>
@@ -9113,10 +9149,14 @@
       </c>
       <c r="M99" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N99" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N99" s="16" t="inlineStr">
+        <is>
+          <t>Indexes in init + integrity migrations (ERD §5) — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O99" s="16" t="inlineStr"/>
       <c r="P99" s="4">
         <f>","&amp;SUBSTITUTE(F99," ","")&amp;","</f>
@@ -9697,12 +9737,12 @@
       </c>
       <c r="M107" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N107" s="16" t="inlineStr">
         <is>
-          <t>docker compose up works (3 healthy); migrations/seed arrive in feature/db-schema</t>
+          <t>Fresh volume: migrate deploy → seed → API healthy; web healthy — feature/db-schema</t>
         </is>
       </c>
       <c r="O107" s="16" t="inlineStr"/>
@@ -9847,10 +9887,14 @@
       </c>
       <c r="M109" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N109" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N109" s="16" t="inlineStr">
+        <is>
+          <t>Versioned migrations; idempotent seed (test/db/seed.test.ts) — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O109" s="16" t="inlineStr"/>
       <c r="P109" s="4">
         <f>","&amp;SUBSTITUTE(F109," ","")&amp;","</f>
@@ -11575,12 +11619,12 @@
       </c>
       <c r="M133" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N133" s="16" t="inlineStr">
         <is>
-          <t>docker-compose.yml and .env.example added; migrations/seed in feature/db-schema</t>
+          <t>docker-compose.yml, .env.example, migrations, persona seed — feature/project-setup, feature/db-schema</t>
         </is>
       </c>
       <c r="O133" s="16" t="inlineStr"/>
@@ -12005,10 +12049,14 @@
       </c>
       <c r="M139" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N139" s="16" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N139" s="16" t="inlineStr">
+        <is>
+          <t>Personas in seed and test helpers — feature/db-schema</t>
+        </is>
+      </c>
       <c r="O139" s="16" t="n"/>
       <c r="P139" s="4">
         <f>","&amp;SUBSTITUTE(F139," ","")&amp;","</f>
@@ -12681,11 +12729,19 @@
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/db/constraints.test.ts</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="33" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -14159,11 +14215,19 @@
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr"/>
-      <c r="K38" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/db/seed.test.ts (automated; no user1/driver1 in seed data)</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
@@ -17459,11 +17523,19 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>e7db6c7 feat(db) schema, 77d5ab5 feat(db) integrity migration, 5c0b0e9 feat(db) helpers — feature/db-schema</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Prisma migrate diff shows no drift against the hand-written objects</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -17496,11 +17568,19 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>b9272b5 feat(seed) — feature/db-schema</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Seed runs on container start; idempotent (TC-37)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="33" customHeight="1">
       <c r="A9" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 1 (feature/db-schema): schema, integrity migration, db helpers, seed, constraint tests</t>
+          <t>2026-09-24 — Phase 2 (feature/passenger-auth): shared schemas, sign-up/sign-in, sessions, guards, rate limit</t>
         </is>
       </c>
     </row>
@@ -1996,10 +1996,14 @@
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N2" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/auth/signup; test/auth/sign-up.test.ts — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O2" s="16" t="inlineStr"/>
       <c r="P2" s="4">
         <f>","&amp;SUBSTITUTE(F2," ","")&amp;","</f>
@@ -2069,10 +2073,14 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N3" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login (e-mail or phone); test/auth/sessions.test.ts — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O3" s="16" t="inlineStr"/>
       <c r="P3" s="4">
         <f>","&amp;SUBSTITUTE(F3," ","")&amp;","</f>
@@ -2142,10 +2150,14 @@
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N4" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/auth/logout revokes the session — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O4" s="16" t="inlineStr"/>
       <c r="P4" s="4">
         <f>","&amp;SUBSTITUTE(F4," ","")&amp;","</f>
@@ -2215,10 +2227,14 @@
       </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N5" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/auth/me (vehicle for drivers) — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O5" s="16" t="inlineStr"/>
       <c r="P5" s="4">
         <f>","&amp;SUBSTITUTE(F5," ","")&amp;","</f>
@@ -2288,10 +2304,14 @@
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>API role guards done (test/auth/access.test.ts); web routing in feature/passenger-ui — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O6" s="16" t="inlineStr"/>
       <c r="P6" s="4">
         <f>","&amp;SUBSTITUTE(F6," ","")&amp;","</f>
@@ -7653,10 +7673,14 @@
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N79" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N79" s="16" t="inlineStr">
+        <is>
+          <t>bcrypt (cost 12; 4 in tests); TC-44 — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O79" s="16" t="inlineStr"/>
       <c r="P79" s="4">
         <f>","&amp;SUBSTITUTE(F79," ","")&amp;","</f>
@@ -7726,10 +7750,14 @@
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N80" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>requireAuth in place; applied to each new endpoint as modules arrive — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O80" s="16" t="inlineStr"/>
       <c r="P80" s="4">
         <f>","&amp;SUBSTITUTE(F80," ","")&amp;","</f>
@@ -7799,10 +7827,14 @@
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N81" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>Role guards done; object-level ownership checks with rides/pools — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O81" s="16" t="inlineStr"/>
       <c r="P81" s="4">
         <f>","&amp;SUBSTITUTE(F81," ","")&amp;","</f>
@@ -7877,7 +7909,7 @@
       </c>
       <c r="N82" s="16" t="inlineStr">
         <is>
-          <t>ZodError → VALIDATION_ERROR mapping in error handler; schemas per endpoint later</t>
+          <t>validateBody with strict shared schemas for auth; other endpoints later — feature/passenger-auth</t>
         </is>
       </c>
       <c r="O82" s="16" t="inlineStr"/>
@@ -8026,12 +8058,12 @@
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N84" s="16" t="inlineStr">
         <is>
-          <t>helmet headers + CORS to WEB_ORIGIN done; session cookie flags in feature/passenger-auth</t>
+          <t>httpOnly SameSite=Lax cookie (Secure via COOKIE_SECURE), helmet, CORS — feature/passenger-auth</t>
         </is>
       </c>
       <c r="O84" s="16" t="inlineStr"/>
@@ -8103,10 +8135,14 @@
       </c>
       <c r="M85" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N85" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>express-rate-limit 10/min per IP; TC-38 — feature/passenger-auth</t>
+        </is>
+      </c>
       <c r="O85" s="16" t="inlineStr"/>
       <c r="P85" s="4">
         <f>","&amp;SUBSTITUTE(F85," ","")&amp;","</f>
@@ -12582,11 +12618,19 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr"/>
-      <c r="K5" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Role part in test/auth/access.test.ts; ride/pool ownership with those modules</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -13913,11 +13957,19 @@
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr"/>
-      <c r="K32" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/auth/sign-up.test.ts</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="33" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
@@ -13962,11 +14014,19 @@
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr"/>
-      <c r="K33" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/auth/sessions.test.ts</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="33" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
@@ -14272,11 +14332,19 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr"/>
-      <c r="K39" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/auth/rate-limit.test.ts</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="33" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
@@ -14566,11 +14634,19 @@
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J45" s="16" t="inlineStr"/>
-      <c r="K45" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/auth/sessions.test.ts (automated: bcrypt hashes, SHA-256 token hash)</t>
+        </is>
+      </c>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="33" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
@@ -14860,11 +14936,19 @@
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J51" s="16" t="inlineStr"/>
-      <c r="K51" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>Part 1 (gender optional at sign-up) in test/auth/sign-up.test.ts; option validation with rides</t>
+        </is>
+      </c>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
@@ -17613,11 +17697,19 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr"/>
-      <c r="I9" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>6ee7875 feat(shared), 0fccd56 feat(auth), 347e153 feat(auth) — feature/passenger-auth</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Sign-up, sign-in, sessions, sign-out, /me</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="33" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -17650,11 +17742,19 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>347e153 feat(auth) guards, cea26a4 feat(auth) rate limit, 07b28b6 test(auth) — feature/passenger-auth</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>requireAuth/requireRole; 10 attempts/min per IP behind one trusted proxy hop</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="33" customHeight="1">
       <c r="A11" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 2 (feature/passenger-auth): shared schemas, sign-up/sign-in, sessions, guards, rate limit</t>
+          <t>2026-09-24 — Phase 3 (feature/zones-fares): fare calculator in paisa, zones and fare-estimate endpoints</t>
         </is>
       </c>
     </row>
@@ -2519,10 +2519,14 @@
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/zones; test/zones/zones.test.ts — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O9" s="16" t="inlineStr"/>
       <c r="P9" s="4">
         <f>","&amp;SUBSTITUTE(F9," ","")&amp;","</f>
@@ -2592,10 +2596,14 @@
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/fares/estimate returns solo and pooled (TC-35); form in feature/passenger-ui — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O10" s="16" t="inlineStr"/>
       <c r="P10" s="4">
         <f>","&amp;SUBSTITUTE(F10," ","")&amp;","</f>
@@ -5167,10 +5175,14 @@
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N45" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>domain/fare.ts computeFare; test/domain/fare.test.ts (TC-03, TC-12) — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O45" s="16" t="inlineStr"/>
       <c r="P45" s="4">
         <f>","&amp;SUBSTITUTE(F45," ","")&amp;","</f>
@@ -5240,10 +5252,14 @@
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N46" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>Estimate returns both figures; stored on the request in feature/ride-request — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O46" s="16" t="inlineStr"/>
       <c r="P46" s="4">
         <f>","&amp;SUBSTITUTE(F46," ","")&amp;","</f>
@@ -5386,10 +5402,14 @@
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N48" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>API returns base, distance charge, discount, seats, total (TC-35); views in the UI branches — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O48" s="16" t="inlineStr"/>
       <c r="P48" s="4">
         <f>","&amp;SUBSTITUTE(F48," ","")&amp;","</f>
@@ -5537,7 +5557,7 @@
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>All money columns BIGINT paisa; formatting in UI later — feature/db-schema</t>
+          <t>BIGINT paisa columns (feature/db-schema); integer-only fare arithmetic in domain/money.ts (feature/zones-fares); display formatting in the UI</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr"/>
@@ -6935,10 +6955,14 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N69" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>zones.service distanceBetween from the seeded table (TC-12) — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O69" s="16" t="inlineStr"/>
       <c r="P69" s="4">
         <f>","&amp;SUBSTITUTE(F69," ","")&amp;","</f>
@@ -7008,10 +7032,14 @@
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N70" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>domain/fare.ts; TC-03, TC-10, TC-12 — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O70" s="16" t="inlineStr"/>
       <c r="P70" s="4">
         <f>","&amp;SUBSTITUTE(F70," ","")&amp;","</f>
@@ -7081,10 +7109,14 @@
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N71" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>FARE_* env rates via config/rules.ts CURRENT_FARE_RATES; base never discounted (test) — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O71" s="16" t="inlineStr"/>
       <c r="P71" s="4">
         <f>","&amp;SUBSTITUTE(F71," ","")&amp;","</f>
@@ -7154,10 +7186,14 @@
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N72" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>computeFare takes the pooled flag (TC-10: 2 seats of 1 passenger not pooled); locking at start in feature/driver-flow — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O72" s="16" t="inlineStr"/>
       <c r="P72" s="4">
         <f>","&amp;SUBSTITUTE(F72," ","")&amp;","</f>
@@ -7227,10 +7263,14 @@
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N73" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>roundHalfUpDiv on the integer remainder; test/domain/money.test.ts — feature/zones-fares</t>
+        </is>
+      </c>
       <c r="O73" s="16" t="inlineStr"/>
       <c r="P73" s="4">
         <f>","&amp;SUBSTITUTE(F73," ","")&amp;","</f>
@@ -7909,7 +7949,7 @@
       </c>
       <c r="N82" s="16" t="inlineStr">
         <is>
-          <t>validateBody with strict shared schemas for auth; other endpoints later — feature/passenger-auth</t>
+          <t>validateBody with strict shared schemas for auth and fare estimates; unexpected fields named in the 400 — feature/zones-fares</t>
         </is>
       </c>
       <c r="O82" s="16" t="inlineStr"/>
@@ -12569,11 +12609,19 @@
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr"/>
-      <c r="K4" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/domain/fare.test.ts</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -12928,11 +12976,19 @@
       </c>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr"/>
-      <c r="K11" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/domain/fare.test.ts (fare level); trip-start check with feature/driver-flow</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="33" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -13026,11 +13082,19 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/domain/fare.test.ts, test/zones/zones.test.ts, test/fares/estimate.test.ts</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="33" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -14177,11 +14241,19 @@
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr"/>
-      <c r="K36" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/zones/zones.test.ts, apps/api/test/fares/estimate.test.ts</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="33" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
@@ -17787,11 +17859,19 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr"/>
-      <c r="I11" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>b4e67b9 feat(fare), 1be55c0 test(fare), d9ff25f test(fare) — feature/zones-fares</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>computeFare() and roundHalfUpDiv() on whole paisa; rates from CURRENT_FARE_RATES</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -17824,11 +17904,19 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>2a5c39d feat(fare), 86a24c5 fix(api), 63be8bb test(fare) — feature/zones-fares</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/zones, POST /api/fares/estimate; zone reference data cached in memory</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="33" customHeight="1">
       <c r="A13" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 3 (feature/zones-fares): fare calculator in paisa, zones and fare-estimate endpoints</t>
+          <t>2026-09-24 — Phase 4 (feature/ride-request): state machines, audit trail, ride requests, expiry, unmatched cancellation</t>
         </is>
       </c>
     </row>
@@ -2673,10 +2673,14 @@
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N11" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/rides; test/rides/request.test.ts (TC-33) — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O11" s="16" t="inlineStr"/>
       <c r="P11" s="4">
         <f>","&amp;SUBSTITUTE(F11," ","")&amp;","</f>
@@ -2746,10 +2750,14 @@
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>409 ACTIVE_REQUEST_EXISTS with the existing ride id; double submit covered (TC-18) — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O12" s="16" t="inlineStr"/>
       <c r="P12" s="4">
         <f>","&amp;SUBSTITUTE(F12," ","")&amp;","</f>
@@ -2819,10 +2827,14 @@
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N13" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>422 INSUFFICIENT_BALANCE against the solo estimate; Rafiq test — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O13" s="16" t="inlineStr"/>
       <c r="P13" s="4">
         <f>","&amp;SUBSTITUTE(F13," ","")&amp;","</f>
@@ -2892,10 +2904,14 @@
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/rides?scope=active and /:id with driver, Tesla, co-rider count, badge — feature/ride-request; screen in feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O14" s="16" t="inlineStr"/>
       <c r="P14" s="4">
         <f>","&amp;SUBSTITUTE(F14," ","")&amp;","</f>
@@ -3038,10 +3054,14 @@
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/rides/:id/cancel: REQUESTED free, STARTED/terminal 409 — feature/ride-request; MATCHED and DRIVER_ARRIVED (fee) later</t>
+        </is>
+      </c>
       <c r="O16" s="16" t="inlineStr"/>
       <c r="P16" s="4">
         <f>","&amp;SUBSTITUTE(F16," ","")&amp;","</f>
@@ -3111,10 +3131,14 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N17" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/rides?scope=history, newest first, cursor paging (TC-39) — feature/ride-request; screen in feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O17" s="16" t="inlineStr"/>
       <c r="P17" s="4">
         <f>","&amp;SUBSTITUTE(F17," ","")&amp;","</f>
@@ -3184,10 +3208,14 @@
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N18" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/rides/:id timeline from status_history — feature/ride-request; screen in feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O18" s="16" t="inlineStr"/>
       <c r="P18" s="4">
         <f>","&amp;SUBSTITUTE(F18," ","")&amp;","</f>
@@ -3257,10 +3285,14 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Option validation (TC-50 parts 2-3) — feature/ride-request; matching in feature/tesla-pooling, badge in the UI</t>
+        </is>
+      </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
           <t>Added in SRS v0.3</t>
@@ -5252,12 +5284,12 @@
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>Estimate returns both figures; stored on the request in feature/ride-request — feature/zones-fares</t>
+          <t>Estimate endpoint (feature/zones-fares); estimated_fare_paisa stored on each request and both figures in the ride view — feature/ride-request</t>
         </is>
       </c>
       <c r="O46" s="16" t="inlineStr"/>
@@ -6071,10 +6103,14 @@
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N57" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N57" s="16" t="inlineStr">
+        <is>
+          <t>recordTransition in the same transaction: ride create, cancel, expiry — feature/ride-request; pool and driver transitions follow</t>
+        </is>
+      </c>
       <c r="O57" s="16" t="inlineStr"/>
       <c r="P57" s="4">
         <f>","&amp;SUBSTITUTE(F57," ","")&amp;","</f>
@@ -6144,12 +6180,12 @@
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N58" s="16" t="inlineStr">
         <is>
-          <t>Append-only trigger tested; audit writer in feature/ride-request — feature/db-schema</t>
+          <t>Append-only trigger (feature/db-schema); audit module has no update/delete path — feature/ride-request</t>
         </is>
       </c>
       <c r="O58" s="16" t="inlineStr"/>
@@ -6221,10 +6257,14 @@
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N59" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>error-handler logs 409/422 at WARN as command.rejected with code and request id — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O59" s="16" t="inlineStr"/>
       <c r="P59" s="4">
         <f>","&amp;SUBSTITUTE(F59," ","")&amp;","</f>
@@ -6294,10 +6334,14 @@
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N60" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Ride, timeline and fare rows readable per ride — feature/ride-request; full E1 reconstruction after feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O60" s="16" t="inlineStr"/>
       <c r="P60" s="4">
         <f>","&amp;SUBSTITUTE(F60," ","")&amp;","</f>
@@ -6659,10 +6703,14 @@
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N65" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Service check plus partial unique index; TC-18 — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O65" s="16" t="inlineStr"/>
       <c r="P65" s="4">
         <f>","&amp;SUBSTITUTE(F65," ","")&amp;","</f>
@@ -6732,10 +6780,14 @@
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N66" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>domain/state-machine.ts over shared transition tables; TC-08 exhaustive — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O66" s="16" t="inlineStr"/>
       <c r="P66" s="4">
         <f>","&amp;SUBSTITUTE(F66," ","")&amp;","</f>
@@ -6882,10 +6934,14 @@
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N68" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>domain/cancellation.ts policy (FREE/FEE/FORBIDDEN); fee charging in feature/driver-flow — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O68" s="16" t="inlineStr"/>
       <c r="P68" s="4">
         <f>","&amp;SUBSTITUTE(F68," ","")&amp;","</f>
@@ -7872,7 +7928,7 @@
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>Role guards done; object-level ownership checks with rides/pools — feature/passenger-auth</t>
+          <t>Role guards (feature/passenger-auth); rides scoped to their owner, 404 for others (TC-04 part) — feature/ride-request</t>
         </is>
       </c>
       <c r="O81" s="16" t="inlineStr"/>
@@ -7949,7 +8005,7 @@
       </c>
       <c r="N82" s="16" t="inlineStr">
         <is>
-          <t>validateBody with strict shared schemas for auth and fare estimates; unexpected fields named in the 400 — feature/zones-fares</t>
+          <t>validateBody with strict shared schemas for auth, estimates and rides; list query parsed with Zod — feature/ride-request</t>
         </is>
       </c>
       <c r="O82" s="16" t="inlineStr"/>
@@ -8479,10 +8535,14 @@
       </c>
       <c r="M89" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N89" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>CAS on status for cancel and expiry, audit in the same transaction — feature/ride-request; accept/pool moves in feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O89" s="16" t="inlineStr"/>
       <c r="P89" s="4">
         <f>","&amp;SUBSTITUTE(F89," ","")&amp;","</f>
@@ -8779,10 +8839,14 @@
       </c>
       <c r="M93" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N93" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N93" s="16" t="inlineStr">
+        <is>
+          <t>Relies on NFR-CON-04: a retry gets 409 ACTIVE_REQUEST_EXISTS with the original ride id — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O93" s="16" t="inlineStr"/>
       <c r="P93" s="4">
         <f>","&amp;SUBSTITUTE(F93," ","")&amp;","</f>
@@ -9079,10 +9143,14 @@
       </c>
       <c r="M97" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N97" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N97" s="16" t="inlineStr">
+        <is>
+          <t>Expiry on read and before every passenger command, plus the 60 s sweep — feature/ride-request; accept check in feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O97" s="16" t="inlineStr"/>
       <c r="P97" s="4">
         <f>","&amp;SUBSTITUTE(F97," ","")&amp;","</f>
@@ -10182,10 +10250,14 @@
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N112" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N112" s="16" t="inlineStr">
+        <is>
+          <t>INFO ride/pool/driver.transition in the audit writer; WARN command.rejected — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O112" s="16" t="inlineStr"/>
       <c r="P112" s="4">
         <f>","&amp;SUBSTITUTE(F112," ","")&amp;","</f>
@@ -10401,10 +10473,14 @@
       </c>
       <c r="M115" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N115" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N115" s="16" t="inlineStr">
+        <is>
+          <t>Pure fare (feature/zones-fares) and transition checks with unit tests (TC-08) — feature/ride-request</t>
+        </is>
+      </c>
       <c r="O115" s="16" t="inlineStr"/>
       <c r="P115" s="4">
         <f>","&amp;SUBSTITUTE(F115," ","")&amp;","</f>
@@ -12560,11 +12636,19 @@
       </c>
       <c r="I3" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr"/>
-      <c r="K3" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>Ride level in test/rides/cancel.test.ts and test/domain/state-machine.test.ts; pool moves later</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
@@ -12671,7 +12755,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>Role part in test/auth/access.test.ts; ride/pool ownership with those modules</t>
+          <t>Roles in test/auth/access.test.ts; ride ownership in test/rides/read.test.ts and cancel.test.ts; pools later</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
@@ -12723,11 +12807,19 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr"/>
-      <c r="K6" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>REQUESTED and STARTED in test/rides/cancel.test.ts, policy in test/domain/cancellation.test.ts; MATCHED and DRIVER_ARRIVED later</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="63" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -12878,11 +12970,19 @@
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr"/>
-      <c r="K9" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/domain/state-machine.test.ts</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="33" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -13384,11 +13484,19 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/rides/request.test.ts (no Idempotency-Key: retries rely on the unique index)</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="33" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
@@ -13678,11 +13786,19 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr"/>
-      <c r="K25" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>Read side in test/rides/read.test.ts; the accept part with feature/tesla-pooling</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="63" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
@@ -14135,11 +14251,19 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr"/>
-      <c r="K34" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/rides/request.test.ts</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="33" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
@@ -14461,11 +14585,19 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr"/>
-      <c r="K40" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/rides/read.test.ts</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="33" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
@@ -15013,7 +15145,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>Part 1 (gender optional at sign-up) in test/auth/sign-up.test.ts; option validation with rides</t>
+          <t>Parts 1-3 in test/auth/sign-up.test.ts and test/rides/request.test.ts; passenger side of part 4 in test/rides/read.test.ts; driver pool response later</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr">
@@ -17949,11 +18081,19 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>97a8fb6 feat(ride) state machines, 97e9a70 feat(audit) — feature/ride-request</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Transition tables shared with the web app; audit writer inside the caller's transaction; WARN log for 409/422</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -17986,11 +18126,19 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr"/>
-      <c r="I14" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>0896c40 feat(ride), e32e7bb fix(ride), dcc02ed feat(ride), 75785c0 test(ride) — feature/ride-request</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Create, list, detail, expiry and REQUESTED cancel done; cancelling MATCHED/DRIVER_ARRIVED (seat release, fee) comes with feature/tesla-pooling and feature/driver-flow</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="33" customHeight="1">
       <c r="A15" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 4 (feature/ride-request): state machines, audit trail, ride requests, expiry, unmatched cancellation</t>
+          <t>2026-09-24 — Phase 5 (feature/tesla-pooling): driver availability and feed, matching, accept with seat locks, matched cancellation, race tests</t>
         </is>
       </c>
     </row>
@@ -3366,10 +3366,14 @@
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/driver/availability returns the Tesla — feature/tesla-pooling; dashboard in feature/driver-ui</t>
+        </is>
+      </c>
       <c r="O20" s="16" t="inlineStr"/>
       <c r="P20" s="4">
         <f>","&amp;SUBSTITUTE(F20," ","")&amp;","</f>
@@ -3439,10 +3443,14 @@
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>PUT /api/driver/availability, audited with the zone (TC-22) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O21" s="16" t="inlineStr"/>
       <c r="P21" s="4">
         <f>","&amp;SUBSTITUTE(F21," ","")&amp;","</f>
@@ -3512,10 +3520,14 @@
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>409 ACTIVE_POOL_EXISTS for offline or zone change during a trip (TC-22) — feature/tesla-pooling; disabled toggle in feature/driver-ui</t>
+        </is>
+      </c>
       <c r="O22" s="16" t="inlineStr"/>
       <c r="P22" s="4">
         <f>","&amp;SUBSTITUTE(F22," ","")&amp;","</f>
@@ -3585,10 +3597,14 @@
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N23" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/driver/requests: zone feed, matching filter with an OPEN pool, 409 DRIVER_OFFLINE (TC-23) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O23" s="16" t="inlineStr"/>
       <c r="P23" s="4">
         <f>","&amp;SUBSTITUTE(F23," ","")&amp;","</f>
@@ -3658,10 +3674,14 @@
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/driver/requests/:id/accept re-checks BR-01…05 in one transaction — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O24" s="16" t="inlineStr"/>
       <c r="P24" s="4">
         <f>","&amp;SUBSTITUTE(F24," ","")&amp;","</f>
@@ -3731,10 +3751,14 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>Pool view (names, seats, status, payment, estimate, badge) returned on accept — feature/tesla-pooling; GET /api/driver/pools and locked fares in feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O25" s="16" t="inlineStr"/>
       <c r="P25" s="4">
         <f>","&amp;SUBSTITUTE(F25," ","")&amp;","</f>
@@ -4315,10 +4339,14 @@
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N33" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Pool created on first accept, audited null → OPEN — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O33" s="16" t="inlineStr"/>
       <c r="P33" s="4">
         <f>","&amp;SUBSTITUTE(F33," ","")&amp;","</f>
@@ -4388,10 +4416,14 @@
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N34" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>Capacity check under the driver and pool locks plus the DB CHECK; TC-01, TC-06 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O34" s="16" t="inlineStr"/>
       <c r="P34" s="4">
         <f>","&amp;SUBSTITUTE(F34," ","")&amp;","</f>
@@ -4461,10 +4493,14 @@
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N35" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>isCompatible at accept time; 422 NOT_COMPATIBLE with reason (TC-20) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O35" s="16" t="inlineStr"/>
       <c r="P35" s="4">
         <f>","&amp;SUBSTITUTE(F35," ","")&amp;","</f>
@@ -4534,10 +4570,14 @@
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N36" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>is_private from the first member; TC-19 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O36" s="16" t="inlineStr"/>
       <c r="P36" s="4">
         <f>","&amp;SUBSTITUTE(F36," ","")&amp;","</f>
@@ -4607,10 +4647,14 @@
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N37" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>409 POOL_NOT_OPEN (TC-21) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O37" s="16" t="inlineStr"/>
       <c r="P37" s="4">
         <f>","&amp;SUBSTITUTE(F37," ","")&amp;","</f>
@@ -4675,15 +4719,19 @@
       </c>
       <c r="L38" s="13" t="inlineStr">
         <is>
-          <t>feature/driver-flow</t>
+          <t>feature/tesla-pooling, feature/driver-flow</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N38" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>MATCHED cancel frees seats at once (TC-16) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O38" s="16" t="inlineStr"/>
       <c r="P38" s="4">
         <f>","&amp;SUBSTITUTE(F38," ","")&amp;","</f>
@@ -4748,15 +4796,19 @@
       </c>
       <c r="L39" s="17" t="inlineStr">
         <is>
-          <t>feature/driver-flow</t>
+          <t>feature/tesla-pooling, feature/driver-flow</t>
         </is>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N39" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>Empty pool cancelled by SYSTEM, ALL_MEMBERS_CANCELLED (TC-16) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O39" s="16" t="inlineStr"/>
       <c r="P39" s="4">
         <f>","&amp;SUBSTITUTE(F39," ","")&amp;","</f>
@@ -4899,12 +4951,12 @@
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>pool_members_one_active_membership index tested; accept flow in feature/tesla-pooling — feature/db-schema</t>
+          <t>Partial unique index (feature/db-schema) and ride CAS; Jashim vs Kamal race 20/20 (TC-06) — feature/tesla-pooling</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr"/>
@@ -4976,12 +5028,12 @@
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
-          <t>pool_members table; roster endpoint in feature/driver-flow — feature/db-schema</t>
+          <t>pool_members rows; driver pool view lists members — feature/tesla-pooling</t>
         </is>
       </c>
       <c r="O42" s="16" t="inlineStr"/>
@@ -5053,10 +5105,14 @@
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N43" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>Restriction checked and updated under the pool lock (TC-47, TC-51) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
           <t>Added in SRS v0.3</t>
@@ -5125,15 +5181,19 @@
       </c>
       <c r="L44" s="13" t="inlineStr">
         <is>
-          <t>feature/driver-flow</t>
+          <t>feature/tesla-pooling, feature/driver-flow</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>Restriction recalculated on leave (TC-49) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
           <t>Added in SRS v0.3</t>
@@ -6411,10 +6471,14 @@
       </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N61" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>TC-01, TC-06 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O61" s="16" t="inlineStr"/>
       <c r="P61" s="4">
         <f>","&amp;SUBSTITUTE(F61," ","")&amp;","</f>
@@ -6484,10 +6548,14 @@
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N62" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>domain/matching.ts; TC-20 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O62" s="16" t="inlineStr"/>
       <c r="P62" s="4">
         <f>","&amp;SUBSTITUTE(F62," ","")&amp;","</f>
@@ -6557,10 +6625,14 @@
       </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N63" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>First accept starts a pool in the driver's zone — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O63" s="16" t="inlineStr"/>
       <c r="P63" s="4">
         <f>","&amp;SUBSTITUTE(F63," ","")&amp;","</f>
@@ -6630,10 +6702,14 @@
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N64" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Driver lock plus pools_one_active_per_driver; TC-19 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O64" s="16" t="inlineStr"/>
       <c r="P64" s="4">
         <f>","&amp;SUBSTITUTE(F64," ","")&amp;","</f>
@@ -7692,10 +7768,14 @@
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N78" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>domain/pool-restriction.ts + matching; TC-47, TC-48, TC-49, TC-51 — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O78" s="16" t="inlineStr">
         <is>
           <t>Added in SRS v0.3</t>
@@ -8462,10 +8542,14 @@
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N88" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>Last-seat race 20/20 in test/pools/concurrency.test.ts (TC-06) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="O88" s="16" t="inlineStr"/>
       <c r="P88" s="4">
         <f>","&amp;SUBSTITUTE(F88," ","")&amp;","</f>
@@ -8540,7 +8624,7 @@
       </c>
       <c r="N89" s="16" t="inlineStr">
         <is>
-          <t>CAS on status for cancel and expiry, audit in the same transaction — feature/ride-request; accept/pool moves in feature/tesla-pooling</t>
+          <t>CAS for cancel, expiry, match and pool cancel; audit in the same transaction; cancel-vs-accept race (TC-17) — feature/tesla-pooling; arrive/start/drop-off in feature/driver-flow</t>
         </is>
       </c>
       <c r="O89" s="16" t="inlineStr"/>
@@ -8612,12 +8696,12 @@
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="N90" s="16" t="inlineStr">
         <is>
-          <t>Mechanism designed: ARCHITECTURE.md §7, ADR-0006</t>
+          <t>Driver and pool row locks plus the CHECK, as in ARCHITECTURE §7 — feature/tesla-pooling; README section in pre-release</t>
         </is>
       </c>
       <c r="O90" s="16" t="inlineStr"/>
@@ -9143,12 +9227,12 @@
       </c>
       <c r="M97" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N97" s="16" t="inlineStr">
         <is>
-          <t>Expiry on read and before every passenger command, plus the 60 s sweep — feature/ride-request; accept check in feature/tesla-pooling</t>
+          <t>Expiry on read, before passenger commands and in the sweep (feature/ride-request); accept refuses expired requests (TC-24) — feature/tesla-pooling</t>
         </is>
       </c>
       <c r="O97" s="16" t="inlineStr"/>
@@ -12587,11 +12671,19 @@
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr"/>
-      <c r="K2" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/accept.test.ts</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="63" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -12812,7 +12904,7 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>REQUESTED and STARTED in test/rides/cancel.test.ts, policy in test/domain/cancellation.test.ts; MATCHED and DRIVER_ARRIVED later</t>
+          <t>REQUESTED, MATCHED (test/pools/leave.test.ts) and STARTED; policy unit test; DRIVER_ARRIVED fee later</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
@@ -12864,11 +12956,19 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr"/>
-      <c r="K7" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/concurrency.test.ts (20 runs each)</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="33" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -13386,11 +13486,19 @@
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/leave.test.ts</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
@@ -13435,11 +13543,19 @@
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/concurrency.test.ts (20 runs, plus a forced accept-first case)</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -13541,11 +13657,19 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr"/>
-      <c r="K20" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/accept.test.ts</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -13590,11 +13714,19 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/domain/matching.test.ts, apps/api/test/pools/accept.test.ts</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="33" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
@@ -13639,11 +13771,19 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr"/>
-      <c r="K22" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/accept.test.ts</t>
+        </is>
+      </c>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="33" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -13688,11 +13828,19 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr"/>
-      <c r="K23" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/drivers/availability.test.ts</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="33" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
@@ -13737,11 +13885,19 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/drivers/feed.test.ts</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="33" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -13786,17 +13942,17 @@
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>Read side in test/rides/read.test.ts; the accept part with feature/tesla-pooling</t>
+          <t>apps/api/test/pools/accept.test.ts, apps/api/test/rides/read.test.ts</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -14993,11 +15149,19 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J48" s="16" t="inlineStr"/>
-      <c r="K48" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/leave.test.ts, apps/api/test/domain/matching.test.ts</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="63" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
@@ -15042,11 +15206,19 @@
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J49" s="16" t="inlineStr"/>
-      <c r="K49" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/leave.test.ts, apps/api/test/domain/matching.test.ts</t>
+        </is>
+      </c>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="33" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
@@ -15091,11 +15263,19 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J50" s="16" t="inlineStr"/>
-      <c r="K50" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/leave.test.ts</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="63" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
@@ -15140,17 +15320,17 @@
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>Parts 1-3 in test/auth/sign-up.test.ts and test/rides/request.test.ts; passenger side of part 4 in test/rides/read.test.ts; driver pool response later</t>
+          <t>test/auth/sign-up.test.ts, test/rides/request.test.ts, test/rides/read.test.ts, test/pools/accept.test.ts (no gender in the driver pool view)</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -15197,11 +15377,19 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J52" s="16" t="inlineStr"/>
-      <c r="K52" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/concurrency.test.ts (20 runs)</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K52"/>
@@ -18136,7 +18324,7 @@
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>Create, list, detail, expiry and REQUESTED cancel done; cancelling MATCHED/DRIVER_ARRIVED (seat release, fee) comes with feature/tesla-pooling and feature/driver-flow</t>
+          <t>Create, list, detail, expiry, REQUESTED and MATCHED cancel done (MATCHED in feature/tesla-pooling); DRIVER_ARRIVED with fee comes with feature/driver-flow</t>
         </is>
       </c>
     </row>
@@ -18171,13 +18359,17 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>c8637c0 feat(driver) — feature/tesla-pooling</t>
+        </is>
+      </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>Moved from feature/driver-flow: accept needs driver availability first (plan Phase 5)</t>
+          <t>GET/PUT /api/driver/availability (audited); GET /api/driver/requests filtered by the matching rule</t>
         </is>
       </c>
     </row>
@@ -18212,11 +18404,19 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>6b23f01 feat(pool) matching, 433fb89 feat(pool) accept, cd60b88 feat(pool) leave — feature/tesla-pooling</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>Accept locks driver → pool → ride; CAS on the ride; CHECK as last defence; restriction under the pool lock; MATCHED cancel frees seats</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="33" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -18249,11 +18449,19 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>1e66ae3 test(pool) — feature/tesla-pooling</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>All races pass 20/20 (TC-06, TC-17, TC-51); README concurrency section is written in pre-release</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="14" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 5 (feature/tesla-pooling): driver availability and feed, matching, accept with seat locks, matched cancellation, race tests</t>
+          <t>2026-09-24 — Phase 6 (feature/driver-flow): arrive, start with fare lock, drop-off, trip cancel, no-show, cancellation fee</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>POST /api/rides/:id/cancel: REQUESTED free, STARTED/terminal 409 — feature/ride-request; MATCHED and DRIVER_ARRIVED (fee) later</t>
+          <t>All states: free in REQUESTED/MATCHED, ৳20 fee in DRIVER_ARRIVED, 409 when started/finished (TC-05) — feature/driver-flow; fee confirmation in feature/passenger-ui</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr"/>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>Pool view (names, seats, status, payment, estimate, badge) returned on accept — feature/tesla-pooling; GET /api/driver/pools and locked fares in feature/driver-flow</t>
+          <t>GET /api/driver/pools?scope=active with names, seats, status, payment, estimate/locked fare, badge — feature/driver-flow; screen in feature/driver-ui</t>
         </is>
       </c>
       <c r="O25" s="16" t="inlineStr"/>
@@ -3828,10 +3828,14 @@
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/arrive — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O26" s="16" t="inlineStr"/>
       <c r="P26" s="4">
         <f>","&amp;SUBSTITUTE(F26," ","")&amp;","</f>
@@ -3901,10 +3905,14 @@
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N27" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/start; refused with nobody on board — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O27" s="16" t="inlineStr"/>
       <c r="P27" s="4">
         <f>","&amp;SUBSTITUTE(F27," ","")&amp;","</f>
@@ -3974,10 +3982,14 @@
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/members/:rideId/complete, any order, auto-complete, zone update (TC-25) — feature/driver-flow; settlement in feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O28" s="16" t="inlineStr"/>
       <c r="P28" s="4">
         <f>","&amp;SUBSTITUTE(F28," ","")&amp;","</f>
@@ -4120,10 +4132,14 @@
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/cancel; members back to REQUESTED free; 409 after start (TC-15) — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O30" s="16" t="inlineStr"/>
       <c r="P30" s="4">
         <f>","&amp;SUBSTITUTE(F30," ","")&amp;","</f>
@@ -4193,10 +4209,14 @@
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/members/:rideId/no-show after NO_SHOW_WAIT_MINUTES, with fee (TC-43) — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O31" s="16" t="inlineStr"/>
       <c r="P31" s="4">
         <f>","&amp;SUBSTITUTE(F31," ","")&amp;","</f>
@@ -4266,10 +4286,14 @@
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N32" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/driver/pools?scope=history, own pools only, with totals (TC-40) — feature/driver-flow; screen in feature/driver-ui</t>
+        </is>
+      </c>
       <c r="O32" s="16" t="inlineStr"/>
       <c r="P32" s="4">
         <f>","&amp;SUBSTITUTE(F32," ","")&amp;","</f>
@@ -4878,10 +4902,14 @@
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>SYSTEM completes the pool after the last drop-off, completed_at set — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O40" s="16" t="inlineStr"/>
       <c r="P40" s="4">
         <f>","&amp;SUBSTITUTE(F40," ","")&amp;","</f>
@@ -5421,10 +5449,14 @@
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N47" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>fares row per on-board member with rate snapshot at start (TC-09, TC-11) — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O47" s="16" t="inlineStr"/>
       <c r="P47" s="4">
         <f>","&amp;SUBSTITUTE(F47," ","")&amp;","</f>
@@ -5499,7 +5531,7 @@
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>API returns base, distance charge, discount, seats, total (TC-35); views in the UI branches — feature/zones-fares</t>
+          <t>API: estimate and locked breakdowns (rides), locked fares per member and totals (driver) — feature/driver-flow; views in the UI branches</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr"/>
@@ -5571,10 +5603,14 @@
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N49" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>CANCELLATION_FEE charge row on passenger cancel after arrival and on no-show — feature/driver-flow</t>
+        </is>
+      </c>
       <c r="O49" s="16" t="inlineStr"/>
       <c r="P49" s="4">
         <f>","&amp;SUBSTITUTE(F49," ","")&amp;","</f>
@@ -6163,12 +6199,12 @@
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
-          <t>recordTransition in the same transaction: ride create, cancel, expiry — feature/ride-request; pool and driver transitions follow</t>
+          <t>Every ride, pool and driver transition audited in its transaction — feature/driver-flow</t>
         </is>
       </c>
       <c r="O57" s="16" t="inlineStr"/>
@@ -7010,12 +7046,12 @@
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N68" s="16" t="inlineStr">
         <is>
-          <t>domain/cancellation.ts policy (FREE/FEE/FORBIDDEN); fee charging in feature/driver-flow — feature/ride-request</t>
+          <t>cancellationPolicy (feature/ride-request); fee recorded after arrival and on no-show; refused once started — feature/driver-flow</t>
         </is>
       </c>
       <c r="O68" s="16" t="inlineStr"/>
@@ -7318,12 +7354,12 @@
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N72" s="16" t="inlineStr">
         <is>
-          <t>computeFare takes the pooled flag (TC-10: 2 seats of 1 passenger not pooled); locking at start in feature/driver-flow — feature/zones-fares</t>
+          <t>pooled = two or more members start together; fare and rates stored at start (TC-09) — feature/driver-flow</t>
         </is>
       </c>
       <c r="O72" s="16" t="inlineStr"/>
@@ -8008,7 +8044,7 @@
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>Role guards (feature/passenger-auth); rides scoped to their owner, 404 for others (TC-04 part) — feature/ride-request</t>
+          <t>Rides scoped to their passenger; driver commands and pool lists scoped to the owning driver, 404 otherwise (TC-04) — feature/driver-flow; wallet later</t>
         </is>
       </c>
       <c r="O81" s="16" t="inlineStr"/>
@@ -8619,12 +8655,12 @@
       </c>
       <c r="M89" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N89" s="16" t="inlineStr">
         <is>
-          <t>CAS for cancel, expiry, match and pool cancel; audit in the same transaction; cancel-vs-accept race (TC-17) — feature/tesla-pooling; arrive/start/drop-off in feature/driver-flow</t>
+          <t>Every transition is a CAS inside a transaction with its side effects and audit row (TC-02, TC-17) — feature/driver-flow</t>
         </is>
       </c>
       <c r="O89" s="16" t="inlineStr"/>
@@ -12728,17 +12764,17 @@
       </c>
       <c r="I3" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J3" s="16" t="inlineStr">
         <is>
-          <t>Ride level in test/rides/cancel.test.ts and test/domain/state-machine.test.ts; pool moves later</t>
+          <t>apps/api/test/pools/cancel-trip.test.ts, trip.test.ts, journey.test.ts, rides/cancel.test.ts, domain/state-machine.test.ts</t>
         </is>
       </c>
       <c r="K3" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12878,17 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>Roles in test/auth/access.test.ts; ride ownership in test/rides/read.test.ts and cancel.test.ts; pools later</t>
+          <t>apps/api/test/pools/cancel-trip.test.ts, rides/read.test.ts, rides/cancel.test.ts, auth/access.test.ts</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -12899,17 +12935,17 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>REQUESTED, MATCHED (test/pools/leave.test.ts) and STARTED; policy unit test; DRIVER_ARRIVED fee later</t>
+          <t>apps/api/test/rides/cancel.test.ts, pools/leave.test.ts, pools/cancel-trip.test.ts, domain/cancellation.test.ts</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -13127,11 +13163,19 @@
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/trip.test.ts</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="33" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -13233,11 +13277,19 @@
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/trip.test.ts</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -13339,11 +13391,19 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/journey.test.ts, rides/read.test.ts</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -13437,11 +13497,19 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/cancel-trip.test.ts</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -13999,11 +14067,19 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr"/>
-      <c r="K26" s="16" t="inlineStr"/>
+          <t>Written</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>Statuses, drop-off order, auto-complete and zone in apps/api/test/pools/journey.test.ts; payments with feature/teslapay-wallet</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 partial</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="33" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -14798,11 +14874,19 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr"/>
-      <c r="K41" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/journey.test.ts, drivers/availability.test.ts</t>
+        </is>
+      </c>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
@@ -14945,11 +15029,19 @@
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/pools/cancel-trip.test.ts</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
@@ -18314,7 +18406,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
@@ -18324,7 +18416,7 @@
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>Create, list, detail, expiry, REQUESTED and MATCHED cancel done (MATCHED in feature/tesla-pooling); DRIVER_ARRIVED with fee comes with feature/driver-flow</t>
+          <t>Create, list, detail, expiry; cancel in REQUESTED, MATCHED (feature/tesla-pooling) and DRIVER_ARRIVED with the fee (feature/driver-flow)</t>
         </is>
       </c>
     </row>
@@ -18494,11 +18586,19 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>f51318f, 3768aad, 12762d8 feat(driver); e03dc7d test(driver) — feature/driver-flow</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>Arrive, start with fare lock, drop-off with auto-complete and zone update, cancel trip, no-show, GET /api/driver/pools</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 6 (feature/driver-flow): arrive, start with fare lock, drop-off, trip cancel, no-show, cancellation fee</t>
+          <t>2026-09-24 — Phase 7 (feature/teslapay-wallet): wallet, top-up, settlement, cash collection, fees, E1–E5 end to end</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>POST /api/pools/:id/members/:rideId/complete, any order, auto-complete, zone update (TC-25) — feature/driver-flow; settlement in feature/teslapay-wallet</t>
+          <t>Drop-off in any order with settlement in the same transaction, auto-complete, zone update (feature/driver-flow, feature/teslapay-wallet)</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr"/>
@@ -4059,10 +4059,14 @@
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N29" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/pools/:id/members/:rideId/cash-collected, once, owner only, PAYMENT audit row (TC-27) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O29" s="16" t="inlineStr"/>
       <c r="P29" s="4">
         <f>","&amp;SUBSTITUTE(F29," ","")&amp;","</f>
@@ -5757,10 +5761,14 @@
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N51" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/wallet and /api/wallet/transactions (newest first, paged) — feature/teslapay-wallet; screen in feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O51" s="16" t="inlineStr"/>
       <c r="P51" s="4">
         <f>","&amp;SUBSTITUTE(F51," ","")&amp;","</f>
@@ -5830,10 +5838,14 @@
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N52" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>POST /api/wallet/topup ৳50–৳5,000, TOPUP ledger entry (TC-29) — feature/teslapay-wallet; 'simulated' label in feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O52" s="16" t="inlineStr"/>
       <c r="P52" s="4">
         <f>","&amp;SUBSTITUTE(F52," ","")&amp;","</f>
@@ -5903,10 +5915,14 @@
       </c>
       <c r="M53" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N53" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>TeslaPay debit at drop-off with RIDE_PAYMENT entry, PAID (TC-26) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O53" s="16" t="inlineStr"/>
       <c r="P53" s="4">
         <f>","&amp;SUBSTITUTE(F53," ","")&amp;","</f>
@@ -5976,10 +5992,14 @@
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N54" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Cash rides PENDING_CASH until collected (TC-27) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O54" s="16" t="inlineStr"/>
       <c r="P54" s="4">
         <f>","&amp;SUBSTITUTE(F54," ","")&amp;","</f>
@@ -6049,10 +6069,14 @@
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N55" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>Fee debited from TeslaPay; UNPAID for cash or a short balance (TC-14) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O55" s="16" t="inlineStr"/>
       <c r="P55" s="4">
         <f>","&amp;SUBSTITUTE(F55," ","")&amp;","</f>
@@ -6122,12 +6146,12 @@
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N56" s="16" t="inlineStr">
         <is>
-          <t>wallets_balance_check + append-only ledger tested; settlement in feature/teslapay-wallet — feature/db-schema</t>
+          <t>CHECK balance &gt;= 0; one ledger entry per change; balance = Σ ledger checked after every wallet test — feature/teslapay-wallet</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr"/>
@@ -6430,12 +6454,12 @@
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>Ride, timeline and fare rows readable per ride — feature/ride-request; full E1 reconstruction after feature/teslapay-wallet</t>
+          <t>E1 reconstructed from ride, pool, fare, payment, ledger and audit rows (TC-30, test/e2e/scenarios.test.ts) — feature/teslapay-wallet</t>
         </is>
       </c>
       <c r="O60" s="16" t="inlineStr"/>
@@ -7585,10 +7609,14 @@
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N75" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>Debit in the drop-off transaction; A-14 fall-back to PENDING_CASH (TC-26) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O75" s="16" t="inlineStr"/>
       <c r="P75" s="4">
         <f>","&amp;SUBSTITUTE(F75," ","")&amp;","</f>
@@ -7658,10 +7686,14 @@
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N76" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>PENDING_CASH → PAID when collected (TC-27) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O76" s="16" t="inlineStr"/>
       <c r="P76" s="4">
         <f>","&amp;SUBSTITUTE(F76," ","")&amp;","</f>
@@ -7731,10 +7763,14 @@
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N77" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>topUpSchema limits, credited at once (TC-29) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O77" s="16" t="inlineStr"/>
       <c r="P77" s="4">
         <f>","&amp;SUBSTITUTE(F77," ","")&amp;","</f>
@@ -8039,12 +8075,12 @@
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N81" s="16" t="inlineStr">
         <is>
-          <t>Rides scoped to their passenger; driver commands and pool lists scoped to the owning driver, 404 otherwise (TC-04) — feature/driver-flow; wallet later</t>
+          <t>Rides, pools, driver lists and wallets are all scoped to their owner; others get 404 or 403 (TC-04) — feature/teslapay-wallet</t>
         </is>
       </c>
       <c r="O81" s="16" t="inlineStr"/>
@@ -8886,10 +8922,14 @@
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N92" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N92" s="16" t="inlineStr">
+        <is>
+          <t>Wallet row locked last; guarded debit; ledger entry in the same transaction; concurrent top-ups and top-up vs fare keep balance = Σ ledger — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O92" s="16" t="inlineStr"/>
       <c r="P92" s="4">
         <f>","&amp;SUBSTITUTE(F92," ","")&amp;","</f>
@@ -9190,10 +9230,14 @@
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N96" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N96" s="16" t="inlineStr">
+        <is>
+          <t>P1001/P1002/P1017 → 503, recovers without restart (TC-42 manual, test/db/errors.test.ts) — feature/teslapay-wallet</t>
+        </is>
+      </c>
       <c r="O96" s="16" t="inlineStr"/>
       <c r="P96" s="4">
         <f>","&amp;SUBSTITUTE(F96," ","")&amp;","</f>
@@ -13448,11 +13492,19 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/wallet/fees.test.ts</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="33" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
@@ -14067,17 +14119,17 @@
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>Statuses, drop-off order, auto-complete and zone in apps/api/test/pools/journey.test.ts; payments with feature/teslapay-wallet</t>
+          <t>apps/api/test/e2e/scenarios.test.ts (E1), apps/api/test/pools/journey.test.ts</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 partial</t>
+          <t>2026-09-24 passing (local + Docker)</t>
         </is>
       </c>
     </row>
@@ -14124,11 +14176,19 @@
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr"/>
-      <c r="K27" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/wallet/settlement.test.ts</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
@@ -14173,11 +14233,19 @@
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr"/>
-      <c r="K28" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/wallet/settlement.test.ts, apps/api/test/e2e/scenarios.test.ts</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="33" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -14222,11 +14290,19 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr"/>
-      <c r="K29" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/wallet/wallet.test.ts</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="33" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
@@ -14271,11 +14347,19 @@
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr"/>
-      <c r="K30" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/wallet/wallet.test.ts</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -14320,11 +14404,19 @@
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr"/>
-      <c r="K31" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>apps/api/test/e2e/scenarios.test.ts (E1 audit rows)</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (local + Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="33" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
@@ -14980,11 +15072,19 @@
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>Manual: docker compose stop db → wallet 503, health 503; start db → 200 without API restart. Mapping in apps/api/test/db/errors.test.ts</t>
+        </is>
+      </c>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-24 passing (manual, Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="33" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
@@ -18631,11 +18731,19 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>a2cba32, a78753d, fc683ad feat(wallet); d2b8f2e test(wallet); e840ff2 test(e2e); cd02042 fix(db) — feature/teslapay-wallet</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>Wallet, statement, top-up; settlement at drop-off with cash fall-back; cash collected; fees charged; E1–E5 end to end</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="33" customHeight="1">
       <c r="A20" s="14" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>0.3 (Draft for review) — see SRS revision history</t>
+          <t>0.4 (Draft for review) — see SRS revision history</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17609,49 +17609,57 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="33" customHeight="1">
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>D-25</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>PRD inconsistency</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>The PRD mandates a master branch, but the repository was initialised with main.</t>
+          <t>The web app uses a neo-brutalist visual style: 3 px black borders, hard offset shadows, flat bold colours with black text, defined once as tokens and a small component kit (ADR-0013).</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Create master and use it as the integration branch (DR-01).</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="n"/>
+          <t>High contrast and visible focus by design (NFR-USA-05), a recognisable look without a library dependency, one place to change the look.</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>Minimal Tailwind with no defined style; a component library (MUI, shadcn/ui)</t>
+        </is>
+      </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>DR-01</t>
+          <t>NFR-USA-01, NFR-USA-02, NFR-USA-05, NFR-USA-06</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I47" s="16" t="n"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>Requested by product owner</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="33" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>P-02</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -17661,18 +17669,18 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>PRD §18 refers to "the concurrency problem in Section 14". It is actually in §12.</t>
+          <t>The PRD mandates a master branch, but the repository was initialised with main.</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Treated as §12.</t>
+          <t>Create master and use it as the integration branch (DR-01).</t>
         </is>
       </c>
       <c r="E48" s="13" t="n"/>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>NFR-CON-01</t>
+          <t>DR-01</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -17690,7 +17698,7 @@
     <row r="49" ht="33" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-02</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -17700,18 +17708,18 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>The PRD lifecycle mixes passenger-level and trip-level states.</t>
+          <t>PRD §18 refers to "the concurrency problem in Section 14". It is actually in §12.</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>Split into two state machines (D-12).</t>
+          <t>Treated as §12.</t>
         </is>
       </c>
       <c r="E49" s="17" t="n"/>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>§5</t>
+          <t>NFR-CON-01</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
@@ -17729,28 +17737,28 @@
     <row r="50" ht="33" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>OI-01</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Open issue</t>
+          <t>PRD inconsistency</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Choose the backend framework, ORM, auth mechanism, test framework, styling and hosting, each justified per DC-07.</t>
+          <t>The PRD lifecycle mixes passenger-level and trip-level states.</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Resolved 2026-09-24: D-14…D-22, ADR-0001…0012</t>
+          <t>Split into two state machines (D-12).</t>
         </is>
       </c>
       <c r="E50" s="13" t="n"/>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>DC-07, DR-07</t>
+          <t>§5</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -17760,7 +17768,7 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I50" s="16" t="n"/>
@@ -17768,7 +17776,7 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>OI-02</t>
+          <t>OI-01</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -17778,18 +17786,18 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Choose the concrete concurrency mechanism (pessimistic SELECT … FOR UPDATE versus a conditional update guarded by CHECK) and document it.</t>
+          <t>Choose the backend framework, ORM, auth mechanism, test framework, styling and hosting, each justified per DC-07.</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>Resolved 2026-09-24: row locks + CAS + constraints in layers (D-18, ADR-0006)</t>
+          <t>Resolved 2026-09-24: D-14…D-22, ADR-0001…0012</t>
         </is>
       </c>
       <c r="E51" s="17" t="n"/>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>NFR-CON-03</t>
+          <t>DC-07, DR-07</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
@@ -17807,7 +17815,7 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>OI-03</t>
+          <t>OI-02</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -17817,31 +17825,70 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>Decide whether the request-expiry sweeper runs as an in-process interval or lazily on read (NFR-REL-04 requires lazy correctness either way).</t>
+          <t>Choose the concrete concurrency mechanism (pessimistic SELECT … FOR UPDATE versus a conditional update guarded by CHECK) and document it.</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Resolved 2026-09-24: expiry checked in accept CAS, plus 60 s in-process sweeper (D-18)</t>
+          <t>Resolved 2026-09-24: row locks + CAS + constraints in layers (D-18, ADR-0006)</t>
         </is>
       </c>
       <c r="E52" s="13" t="n"/>
       <c r="F52" s="13" t="inlineStr">
         <is>
+          <t>NFR-CON-03</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>OI-03</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>Open issue</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>Decide whether the request-expiry sweeper runs as an in-process interval or lazily on read (NFR-REL-04 requires lazy correctness either way).</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>Resolved 2026-09-24: expiry checked in accept CAS, plus 60 s in-process sweeper (D-18)</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
           <t>NFR-REL-04</t>
         </is>
       </c>
-      <c r="G52" s="15" t="inlineStr">
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="I52" s="16" t="n"/>
+      <c r="I53" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I52"/>

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 — Phase 7 (feature/teslapay-wallet): wallet, top-up, settlement, cash collection, fees, E1–E5 end to end</t>
+          <t>2026-09-25 — Phase 8 (feature/passenger-ui): UI kit, auth pages, ride request, live tracker, history, ride detail, TeslaPay wallet</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
-          <t>API role guards done (test/auth/access.test.ts); web routing in feature/passenger-ui — feature/passenger-auth</t>
+          <t>API role guards (test/auth/access.test.ts); web group layouts redirect by role via lib/server-session.ts — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O6" s="16" t="inlineStr"/>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
-          <t>POST /api/fares/estimate returns solo and pooled (TC-35); form in feature/passenger-ui — feature/zones-fares</t>
+          <t>POST /api/fares/estimate (TC-35); /ride shows solo and shared prices as the trip is chosen — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O10" s="16" t="inlineStr"/>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N14" s="16" t="inlineStr">
         <is>
-          <t>GET /api/rides?scope=active and /:id with driver, Tesla, co-rider count, badge — feature/ride-request; screen in feature/passenger-ui</t>
+          <t>Ride tracker: status stepper, driver, Tesla and plate, co-rider count, restriction badge — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O14" s="16" t="inlineStr"/>
@@ -2981,10 +2981,14 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>useActiveRide/useRide refresh every 4 s while active, no reload needed — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O15" s="16" t="inlineStr"/>
       <c r="P15" s="4">
         <f>","&amp;SUBSTITUTE(F15," ","")&amp;","</f>
@@ -3054,12 +3058,12 @@
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N16" s="16" t="inlineStr">
         <is>
-          <t>All states: free in REQUESTED/MATCHED, ৳20 fee in DRIVER_ARRIVED, 409 when started/finished (TC-05) — feature/driver-flow; fee confirmation in feature/passenger-ui</t>
+          <t>API rules (TC-05, feature/driver-flow); cancel dialog states free or the ৳20 fee before confirming — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O16" s="16" t="inlineStr"/>
@@ -3131,12 +3135,12 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N17" s="16" t="inlineStr">
         <is>
-          <t>GET /api/rides?scope=history, newest first, cursor paging (TC-39) — feature/ride-request; screen in feature/passenger-ui</t>
+          <t>GET /api/rides?scope=history (TC-39); /rides paged list with Show more — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O17" s="16" t="inlineStr"/>
@@ -3208,12 +3212,12 @@
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>GET /api/rides/:id timeline from status_history — feature/ride-request; screen in feature/passenger-ui</t>
+          <t>GET /api/rides/:id; /rides/[id] timeline from status_history and fare breakdown — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O18" s="16" t="inlineStr"/>
@@ -3285,12 +3289,12 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>Option validation (TC-50 parts 2-3) — feature/ride-request; matching in feature/tesla-pooling, badge in the UI</t>
+          <t>Validation (TC-50), matching (feature/tesla-pooling); same-gender toggle and Women-only/Men-only badge — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O19" s="16" t="inlineStr">
@@ -5535,7 +5539,7 @@
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>API: estimate and locked breakdowns (rides), locked fares per member and totals (driver) — feature/driver-flow; views in the UI branches</t>
+          <t>Passenger views show the estimate and locked breakdowns (FareBreakdown) — feature/passenger-ui; driver views in feature/driver-ui</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr"/>
@@ -5684,12 +5688,12 @@
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>BIGINT paisa columns (feature/db-schema); integer-only fare arithmetic in domain/money.ts (feature/zones-fares); display formatting in the UI</t>
+          <t>BIGINT paisa columns (feature/db-schema); integer arithmetic (domain/money.ts); display only via formatPaisa / MoneyText — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr"/>
@@ -5761,12 +5765,12 @@
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>GET /api/wallet and /api/wallet/transactions (newest first, paged) — feature/teslapay-wallet; screen in feature/passenger-ui</t>
+          <t>GET /api/wallet, /api/wallet/transactions; /wallet balance and paged statement — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O51" s="16" t="inlineStr"/>
@@ -5838,12 +5842,12 @@
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>POST /api/wallet/topup ৳50–৳5,000, TOPUP ledger entry (TC-29) — feature/teslapay-wallet; 'simulated' label in feature/passenger-ui</t>
+          <t>POST /api/wallet/topup (TC-29); /wallet top-up in taka, labelled simulated — feature/passenger-ui</t>
         </is>
       </c>
       <c r="O52" s="16" t="inlineStr"/>
@@ -9534,10 +9538,14 @@
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N100" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N100" s="16" t="inlineStr">
+        <is>
+          <t>refetchInterval 4 s while active, stops when terminal, paused while the tab is hidden — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O100" s="16" t="inlineStr"/>
       <c r="P100" s="4">
         <f>","&amp;SUBSTITUTE(F100," ","")&amp;","</f>
@@ -9607,10 +9615,14 @@
       </c>
       <c r="M101" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N101" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N101" s="16" t="inlineStr">
+        <is>
+          <t>LoadingState, EmptyState, ErrorState with retry on every query-driven passenger view — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O101" s="16" t="inlineStr"/>
       <c r="P101" s="4">
         <f>","&amp;SUBSTITUTE(F101," ","")&amp;","</f>
@@ -9680,10 +9692,14 @@
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N102" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N102" s="16" t="inlineStr">
+        <is>
+          <t>lib/labels.ts human labels; StatusStepper and ride timeline — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O102" s="16" t="inlineStr"/>
       <c r="P102" s="4">
         <f>","&amp;SUBSTITUTE(F102," ","")&amp;","</f>
@@ -9753,10 +9769,14 @@
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N103" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N103" s="16" t="inlineStr">
+        <is>
+          <t>Cancel shown only when the API allows it — feature/passenger-ui; driver actions in feature/driver-ui</t>
+        </is>
+      </c>
       <c r="O103" s="16" t="inlineStr"/>
       <c r="P103" s="4">
         <f>","&amp;SUBSTITUTE(F103," ","")&amp;","</f>
@@ -9826,10 +9846,14 @@
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N104" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N104" s="16" t="inlineStr">
+        <is>
+          <t>MoneyText/formatPaisa ৳ with two decimals; breakdown on the tracker and ride detail — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O104" s="16" t="inlineStr"/>
       <c r="P104" s="4">
         <f>","&amp;SUBSTITUTE(F104," ","")&amp;","</f>
@@ -9899,10 +9923,14 @@
       </c>
       <c r="M105" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N105" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N105" s="16" t="inlineStr">
+        <is>
+          <t>Labelled controls, thick focus outlines, black-on-accent contrast (ADR-0013), 360 px layout — feature/passenger-ui</t>
+        </is>
+      </c>
       <c r="O105" s="16" t="inlineStr"/>
       <c r="P105" s="4">
         <f>","&amp;SUBSTITUTE(F105," ","")&amp;","</f>
@@ -9972,10 +10000,14 @@
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N106" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N106" s="16" t="inlineStr">
+        <is>
+          <t>Cancel-ride ConfirmDialog states the fee — feature/passenger-ui; cancel pool in feature/driver-ui</t>
+        </is>
+      </c>
       <c r="O106" s="16" t="inlineStr"/>
       <c r="P106" s="4">
         <f>","&amp;SUBSTITUTE(F106," ","")&amp;","</f>
@@ -18823,11 +18855,19 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr"/>
-      <c r="I20" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>4146169 docs(adr); 8d69a7d, e044886, 79c3d62 feat(web) — feature/passenger-ui</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>ADR-0013 and the neo-brutalist UI kit; API client and query setup; sign-in, sign-up, role routing, shared loading/empty/error states</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -18860,11 +18900,19 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr"/>
-      <c r="I21" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>426e79b feat(web); 7c08021 feat(ride); a89a16b feat(web) — feature/passenger-ui</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>Request form with live solo/shared estimate and same-gender option; live tracker polling every 4 s; cancel dialog stating the fee (API now reports whether and at what cost a ride can be cancelled)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="33" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
@@ -18897,11 +18945,19 @@
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr"/>
-      <c r="I22" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>feat(web): add ride history, ride detail and wallet pages — feature/passenger-ui</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>Paged ride history; ride detail with timeline and fare breakdown; TeslaPay balance, simulated top-up in taka, paged statement</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="9" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 — Phase 8 (feature/passenger-ui): UI kit, auth pages, ride request, live tracker, history, ride detail, TeslaPay wallet</t>
+          <t>2026-09-25 — Phase 9 (feature/driver-ui): driver dashboard, request feed, active trip management, trip history</t>
         </is>
       </c>
     </row>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>GET /api/driver/availability returns the Tesla — feature/tesla-pooling; dashboard in feature/driver-ui</t>
+          <t>GET /api/driver/availability (feature/tesla-pooling); /driver shows the Tesla, plate, seats and status — feature/driver-ui</t>
         </is>
       </c>
       <c r="O20" s="16" t="inlineStr"/>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N22" s="16" t="inlineStr">
         <is>
-          <t>409 ACTIVE_POOL_EXISTS for offline or zone change during a trip (TC-22) — feature/tesla-pooling; disabled toggle in feature/driver-ui</t>
+          <t>409 ACTIVE_POOL_EXISTS (TC-22, feature/tesla-pooling); zone and online toggle locked with the reason during a trip — feature/driver-ui</t>
         </is>
       </c>
       <c r="O22" s="16" t="inlineStr"/>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>GET /api/driver/pools?scope=active with names, seats, status, payment, estimate/locked fare, badge — feature/driver-flow; screen in feature/driver-ui</t>
+          <t>GET /api/driver/pools?scope=active (feature/driver-flow); /driver/pool shows names, seats, status, payment, estimate or fixed fare, badges — feature/driver-ui</t>
         </is>
       </c>
       <c r="O25" s="16" t="inlineStr"/>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>GET /api/driver/pools?scope=history, own pools only, with totals (TC-40) — feature/driver-flow; screen in feature/driver-ui</t>
+          <t>GET /api/driver/pools?scope=history (TC-40, feature/driver-flow); /driver/history paged with fares and payments — feature/driver-ui</t>
         </is>
       </c>
       <c r="O32" s="16" t="inlineStr"/>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>Passenger views show the estimate and locked breakdowns (FareBreakdown) — feature/passenger-ui; driver views in feature/driver-ui</t>
+          <t>Passenger breakdowns (feature/passenger-ui); per-passenger and trip totals on the driver screens — feature/driver-ui</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr"/>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="M103" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N103" s="16" t="inlineStr">
         <is>
-          <t>Cancel shown only when the API allows it — feature/passenger-ui; driver actions in feature/driver-ui</t>
+          <t>Passenger Cancel from the API's cancellation (feature/passenger-ui); driver buttons from the shared transition tables via lib/driver-moves.ts — feature/driver-ui</t>
         </is>
       </c>
       <c r="O103" s="16" t="inlineStr"/>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N106" s="16" t="inlineStr">
         <is>
-          <t>Cancel-ride ConfirmDialog states the fee — feature/passenger-ui; cancel pool in feature/driver-ui</t>
+          <t>Cancel ride states the fee (feature/passenger-ui); Cancel trip and No-show confirm and say who is charged — feature/driver-ui</t>
         </is>
       </c>
       <c r="O106" s="16" t="inlineStr"/>
@@ -18990,11 +18990,19 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr"/>
-      <c r="I23" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>481d4bc, e307a78, ed3573c, e6f8b8c feat(web); dd24095 refactor(web) — feature/driver-ui</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>Dashboard with zone and online toggle (locked during a trip); request feed with accept; active trip screen with transition-driven buttons; trip history with cash collection</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="33" customHeight="1">
       <c r="A24" s="14" t="inlineStr">

--- a/docs/DhakaPool_SRS_Tracker.xlsx
+++ b/docs/DhakaPool_SRS_Tracker.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 — Phase 9 (feature/driver-ui): driver dashboard, request feed, active trip management, trip history</t>
+          <t>2026-09-25 — Phase 10 (pre-release): fresh-clone fixes, load smoke test, README, scaling notes, deployment configuration; requirements with passing tests marked Verified</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N2" s="16" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N3" s="16" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N4" s="16" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N5" s="16" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N6" s="16" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N7" s="16" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N9" s="16" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N10" s="16" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N11" s="16" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N12" s="16" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N13" s="16" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N14" s="16" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N16" s="16" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N17" s="16" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N20" s="16" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N21" s="16" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N22" s="16" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N23" s="16" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N24" s="16" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N25" s="16" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N26" s="16" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N27" s="16" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N28" s="16" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N29" s="16" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N30" s="16" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N31" s="16" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N32" s="16" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N33" s="16" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N34" s="16" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N35" s="16" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N36" s="16" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N37" s="16" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N38" s="16" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N39" s="16" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N40" s="16" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N41" s="16" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N42" s="16" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N43" s="16" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N44" s="16" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N45" s="16" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N46" s="16" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N47" s="16" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N48" s="16" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N49" s="16" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N50" s="16" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N51" s="16" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N52" s="16" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="M53" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N53" s="16" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N54" s="16" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N55" s="16" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N56" s="16" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N57" s="16" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N58" s="16" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N59" s="16" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N60" s="16" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N61" s="16" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N62" s="16" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N63" s="16" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N64" s="16" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N65" s="16" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N66" s="16" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N67" s="16" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N68" s="16" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N69" s="16" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N70" s="16" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N71" s="16" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N72" s="16" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N73" s="16" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N74" s="16" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N75" s="16" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N76" s="16" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N77" s="16" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N78" s="16" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N79" s="16" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N80" s="16" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N81" s="16" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N82" s="16" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N83" s="16" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N84" s="16" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="M85" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N85" s="16" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N86" s="16" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="M87" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N87" s="16" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N88" s="16" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="M89" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N89" s="16" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N90" s="16" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M91" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N91" s="16" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N92" s="16" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="M93" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N93" s="16" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N94" s="16" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="M95" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N95" s="16" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N96" s="16" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="M97" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N97" s="16" t="inlineStr">
@@ -9388,10 +9388,14 @@
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N98" s="16" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="N98" s="16" t="inlineStr">
+        <is>
+          <t>npm run load:smoke: p95 26.5 ms, 0 failed (TC-46) — pre-release</t>
+        </is>
+      </c>
       <c r="O98" s="16" t="inlineStr"/>
       <c r="P98" s="4">
         <f>","&amp;SUBSTITUTE(F98," ","")&amp;","</f>
@@ -10077,7 +10081,7 @@
       </c>
       <c r="M107" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N107" s="16" t="inlineStr">
@@ -10227,7 +10231,7 @@
       </c>
       <c r="M109" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N109" s="16" t="inlineStr">
@@ -10300,10 +10304,14 @@
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N110" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N110" s="16" t="inlineStr">
+        <is>
+          <t>render.yaml, apps/web/vercel.json, README Deployment; Docker Compose fallback verified (TC-36) — pre-release</t>
+        </is>
+      </c>
       <c r="O110" s="16" t="inlineStr"/>
       <c r="P110" s="4">
         <f>","&amp;SUBSTITUTE(F110," ","")&amp;","</f>
@@ -10373,7 +10381,7 @@
       </c>
       <c r="M111" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N111" s="16" t="inlineStr">
@@ -10592,7 +10600,7 @@
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N114" s="16" t="inlineStr">
@@ -10669,7 +10677,7 @@
       </c>
       <c r="M115" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N115" s="16" t="inlineStr">
@@ -10815,12 +10823,12 @@
       </c>
       <c r="M117" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N117" s="16" t="inlineStr">
         <is>
-          <t>npm test at root and in Docker (docker compose run --rm api npm test)</t>
+          <t>npm test at the root; docker compose run --rm api npm test (231 passing in a fresh clone) — pre-release</t>
         </is>
       </c>
       <c r="O117" s="16" t="inlineStr"/>
@@ -11107,10 +11115,14 @@
       </c>
       <c r="M121" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N121" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N121" s="16" t="inlineStr">
+        <is>
+          <t>Vercel Hobby, Render free, Supabase free; Railway rejected because its free plan cannot run a service — pre-release</t>
+        </is>
+      </c>
       <c r="O121" s="16" t="inlineStr"/>
       <c r="P121" s="4">
         <f>","&amp;SUBSTITUTE(F121," ","")&amp;","</f>
@@ -11322,10 +11334,14 @@
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N124" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N124" s="16" t="inlineStr">
+        <is>
+          <t>README 'Tech stack and why' table, one ADR per choice — pre-release</t>
+        </is>
+      </c>
       <c r="O124" s="16" t="inlineStr"/>
       <c r="P124" s="4">
         <f>","&amp;SUBSTITUTE(F124," ","")&amp;","</f>
@@ -11391,10 +11407,14 @@
       </c>
       <c r="M125" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N125" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N125" s="16" t="inlineStr">
+        <is>
+          <t>master and pre-release exist; release/v1.0.0 is cut in the release step — pre-release</t>
+        </is>
+      </c>
       <c r="O125" s="16" t="inlineStr"/>
       <c r="P125" s="4">
         <f>","&amp;SUBSTITUTE(F125," ","")&amp;","</f>
@@ -11460,12 +11480,12 @@
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N126" s="16" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md §3–4, §12; docs/ERD.md §1</t>
+          <t>feature/* branches merged through PRs #1–#10</t>
         </is>
       </c>
       <c r="O126" s="16" t="inlineStr"/>
@@ -11533,12 +11553,12 @@
       </c>
       <c r="M127" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N127" s="16" t="inlineStr">
         <is>
-          <t>docs/adr/0001–0012 (README summary pending, T-24)</t>
+          <t>Every commit follows &lt;type&gt;(&lt;scope&gt;): &lt;description&gt; (checked with git log; only GitHub's 'Initial commit' differs)</t>
         </is>
       </c>
       <c r="O127" s="16" t="inlineStr"/>
@@ -11606,10 +11626,14 @@
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N128" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N128" s="16" t="inlineStr">
+        <is>
+          <t>Incremental commits across 13 feature branches, each merged when it worked</t>
+        </is>
+      </c>
       <c r="O128" s="16" t="inlineStr"/>
       <c r="P128" s="4">
         <f>","&amp;SUBSTITUTE(F128," ","")&amp;","</f>
@@ -11679,10 +11703,14 @@
       </c>
       <c r="M129" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N129" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N129" s="16" t="inlineStr">
+        <is>
+          <t>README (8bbd6f6); AI Usage section and video link still to add — pre-release</t>
+        </is>
+      </c>
       <c r="O129" s="16" t="inlineStr"/>
       <c r="P129" s="4">
         <f>","&amp;SUBSTITUTE(F129," ","")&amp;","</f>
@@ -11748,12 +11776,12 @@
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N130" s="16" t="inlineStr">
         <is>
-          <t>docs/ARCHITECTURE.md §3–4, §12; docs/ERD.md §1</t>
+          <t>docs/ARCHITECTURE.md §3–4, docs/ERD.md §1, both embedded in the README</t>
         </is>
       </c>
       <c r="O130" s="16" t="inlineStr"/>
@@ -11821,12 +11849,12 @@
       </c>
       <c r="M131" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N131" s="16" t="inlineStr">
         <is>
-          <t>docs/adr/0001–0012 (README summary pending, T-24)</t>
+          <t>README 'Tech stack and why' + docs/adr/0001–0013 (all Accepted)</t>
         </is>
       </c>
       <c r="O131" s="16" t="inlineStr"/>
@@ -11894,10 +11922,14 @@
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N132" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N132" s="16" t="inlineStr">
+        <is>
+          <t>Drafted; awaiting the author's wording — pre-release</t>
+        </is>
+      </c>
       <c r="O132" s="16" t="inlineStr"/>
       <c r="P132" s="4">
         <f>","&amp;SUBSTITUTE(F132," ","")&amp;","</f>
@@ -11967,7 +11999,7 @@
       </c>
       <c r="M133" s="15" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N133" s="16" t="inlineStr">
@@ -12040,10 +12072,14 @@
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N134" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N134" s="16" t="inlineStr">
+        <is>
+          <t>The six PRD §12 areas are tested (README 'Tests'; TC-01…TC-06 passing)</t>
+        </is>
+      </c>
       <c r="O134" s="16" t="inlineStr"/>
       <c r="P134" s="4">
         <f>","&amp;SUBSTITUTE(F134," ","")&amp;","</f>
@@ -12113,10 +12149,14 @@
       </c>
       <c r="M135" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N135" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="N135" s="16" t="inlineStr">
+        <is>
+          <t>Deployment configuration and steps (7ce300f); URL added once live — pre-release</t>
+        </is>
+      </c>
       <c r="O135" s="16" t="inlineStr"/>
       <c r="P135" s="4">
         <f>","&amp;SUBSTITUTE(F135," ","")&amp;","</f>
@@ -12251,10 +12291,14 @@
       </c>
       <c r="M137" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N137" s="16" t="inlineStr"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N137" s="16" t="inlineStr">
+        <is>
+          <t>Free tiers only; .env git-ignored; .env.example has placeholders only</t>
+        </is>
+      </c>
       <c r="O137" s="16" t="inlineStr"/>
       <c r="P137" s="4">
         <f>","&amp;SUBSTITUTE(F137," ","")&amp;","</f>
@@ -12320,12 +12364,12 @@
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N138" s="16" t="inlineStr">
         <is>
-          <t>SRS v0.2 revision 2026-09-24</t>
+          <t>No queue, cache, microservice or Kubernetes (README, ADR-0001); docs/SCALING.md says when each would be worth it</t>
         </is>
       </c>
       <c r="O138" s="16" t="inlineStr"/>
@@ -12397,12 +12441,12 @@
       </c>
       <c r="M139" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="N139" s="16" t="inlineStr">
         <is>
-          <t>Personas in seed and test helpers — feature/db-schema</t>
+          <t>Personas in seed, tests, README and UI (TC-37)</t>
         </is>
       </c>
       <c r="O139" s="16" t="n"/>
@@ -12470,10 +12514,14 @@
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N140" s="16" t="n"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N140" s="16" t="inlineStr">
+        <is>
+          <t>README 'Concurrency: the last-seat problem' — pre-release</t>
+        </is>
+      </c>
       <c r="O140" s="16" t="n"/>
       <c r="P140" s="4">
         <f>","&amp;SUBSTITUTE(F140," ","")&amp;","</f>
@@ -12539,10 +12587,14 @@
       </c>
       <c r="M141" s="15" t="inlineStr">
         <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="N141" s="16" t="n"/>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="N141" s="16" t="inlineStr">
+        <is>
+          <t>docs/SCALING.md (3228d36) — pre-release</t>
+        </is>
+      </c>
       <c r="O141" s="16" t="n"/>
       <c r="P141" s="4">
         <f>","&amp;SUBSTITUTE(F141," ","")&amp;","</f>
@@ -12608,12 +12660,12 @@
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="N142" s="16" t="inlineStr">
         <is>
-          <t>SRS v0.2 revision 2026-09-24</t>
+          <t>SRS v0.5 baseline; tracker updated in every branch</t>
         </is>
       </c>
       <c r="O142" s="16" t="n"/>
@@ -14664,17 +14716,17 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>Written</t>
+          <t>Passing</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>apps/api/test/app.test.ts (404, malformed JSON, requestId); 409/500 cases added with later modules</t>
+          <t>apps/api/test/app.test.ts (404, malformed JSON, forced 500 without details, requestId); 409/422 across the module tests</t>
         </is>
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>2026-09-24 passing</t>
+          <t>2026-09-25 passing</t>
         </is>
       </c>
     </row>
@@ -14778,11 +14830,19 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr"/>
-      <c r="K37" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>Manual: fresh clone of pre-release, cp .env.example .env, docker compose up --build → db, api, web healthy; migrations + seed applied; personas sign in; 231 API tests pass inside Docker</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-25 passing (Docker)</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="33" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
@@ -15275,11 +15335,19 @@
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr"/>
-      <c r="K46" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>Inspection: every money column is BigInt (schema.prisma; Decimal only for zone lat/lng); fare arithmetic is integer (domain/money.ts roundHalfUpDiv); display only via formatPaisa</t>
+        </is>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-25 passing (inspection)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="33" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
@@ -15324,11 +15392,19 @@
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>Not Written</t>
-        </is>
-      </c>
-      <c r="J47" s="16" t="inlineStr"/>
-      <c r="K47" s="16" t="inlineStr"/>
+          <t>Passing</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>scripts/load-smoke.mjs (npm run load:smoke): 20 users × 60 s, 87,367 requests, 0 failed, p95 26.5 ms</t>
+        </is>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-25 passing (fresh Docker stack)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
@@ -19035,11 +19111,19 @@
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr"/>
-      <c r="I24" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>67fb6fb fix(env), d1d7715 fix(docker), 5d65a4c fix(api), fc2f4f1 fix(db); d5293e7 test(perf); ca81bb9 test(api) — pre-release</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>Fresh-clone Docker run (TC-36) found the unquoted demo password and the missing OpenSSL; deployment review found the proxy hop count and the unused DIRECT_URL. Load smoke p95 26.5 ms. Browser walkthrough (TC-41) still to do.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="33" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -19072,11 +19156,19 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr"/>
-      <c r="I25" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>8bbd6f6 docs(readme) — pre-release</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>Everything except the AI Usage section (awaiting the author's wording) and the demo video link (release)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="33" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
@@ -19109,11 +19201,19 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr"/>
-      <c r="I26" s="16" t="inlineStr"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>7ce300f build(deploy) — pre-release</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>render.yaml + apps/web/vercel.json + README steps; Railway's free plan cannot run a service, so Render (ADR-0009 fallback). Live URL once the accounts are set up</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="33" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -19146,11 +19246,19 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr"/>
-      <c r="I27" s="16" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>3228d36 docs(scaling) — pre-release</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>docs/SCALING.md with load estimate, target architecture and diagram</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="33" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
